--- a/02.需求分析/第17小组_基于AI 智能体的康养系统_需求跟踪矩阵.xlsx
+++ b/02.需求分析/第17小组_基于AI 智能体的康养系统_需求跟踪矩阵.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="486" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" tabRatio="486" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" state="visible" r:id="rId1"/>
@@ -157,7 +157,7 @@
     <definedName name="状态">[20]分类数据!$G$3:$G$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'设计用RTM'!$4:$5</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -172,7 +172,7 @@
     <numFmt numFmtId="169" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="170" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="42">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -181,100 +181,110 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="黑体"/>
       <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <color indexed="10"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <color indexed="12"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="MS PGothic"/>
-      <charset val="134"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <color indexed="10"/>
       <sz val="10"/>
     </font>
@@ -286,26 +296,29 @@
     <font>
       <name val="幼圆"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="黑体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <i val="1"/>
       <color indexed="12"/>
@@ -329,178 +342,29 @@
     <font>
       <name val="幼圆"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="MS Sans Serif"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
       <sz val="8"/>
     </font>
     <font>
@@ -512,12 +376,13 @@
     </font>
     <font>
       <name val="Helv"/>
-      <charset val="134"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="黑体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="12"/>
     </font>
     <font>
@@ -533,20 +398,28 @@
     </font>
     <font>
       <name val="MS Mincho"/>
-      <charset val="134"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -571,194 +444,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="51">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1268,104 +955,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1417,187 +1006,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="73">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="38" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="39" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="40" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="41" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="42" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="41" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="43" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="45" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="25">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="15" fontId="50" fillId="0" borderId="0"/>
+    <xf numFmtId="15" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="46" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="38" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="36" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="36" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1639,7 +1084,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1648,32 +1093,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="59">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1686,7 +1123,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1707,7 +1144,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1734,7 +1171,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1749,7 +1186,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1787,19 +1224,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="60">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="58">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1827,13 +1264,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="58">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="58">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="58">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1992,13 +1429,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2008,44 +1439,70 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="13">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="61">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2073,97 +1530,46 @@
     <xf numFmtId="165" fontId="16" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="73">
+  <cellStyles count="25">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Calc Currency (0)" xfId="49"/>
-    <cellStyle name="Date" xfId="50"/>
-    <cellStyle name="Euro" xfId="51"/>
-    <cellStyle name="Header1" xfId="52"/>
-    <cellStyle name="Header2" xfId="53"/>
-    <cellStyle name="New Times Roman" xfId="54"/>
-    <cellStyle name="Normal_#10-Headcount" xfId="55"/>
-    <cellStyle name="標準_(D)日程計画" xfId="56"/>
-    <cellStyle name="表示済みのハイパーリンク_02_1st_2ndOTP対応機能一覧_一応完成版" xfId="57"/>
-    <cellStyle name="常规_GM09MR_RTM_DisplayAPP_Sub_C" xfId="58"/>
-    <cellStyle name="常规_Sheet4" xfId="59"/>
-    <cellStyle name="常规_需求跟踪矩阵" xfId="60"/>
-    <cellStyle name="常规_需求跟踪矩阵模板" xfId="61"/>
-    <cellStyle name="段落标题1" xfId="62"/>
-    <cellStyle name="段落标题2" xfId="63"/>
-    <cellStyle name="桁区切り [0.00]_(D)日程計画" xfId="64"/>
-    <cellStyle name="桁区切り_(D)日程計画" xfId="65"/>
-    <cellStyle name="普通_laroux" xfId="66"/>
-    <cellStyle name="千位[0]_laroux" xfId="67"/>
-    <cellStyle name="千位_laroux" xfId="68"/>
-    <cellStyle name="通貨 [0.00]_(D)日程計画" xfId="69"/>
-    <cellStyle name="通貨_(D)日程計画" xfId="70"/>
-    <cellStyle name="样式 1" xfId="71"/>
-    <cellStyle name="표준_Book1" xfId="72"/>
+    <cellStyle name="Calc Currency (0)" xfId="1"/>
+    <cellStyle name="Date" xfId="2"/>
+    <cellStyle name="Euro" xfId="3"/>
+    <cellStyle name="Header1" xfId="4"/>
+    <cellStyle name="Header2" xfId="5"/>
+    <cellStyle name="New Times Roman" xfId="6"/>
+    <cellStyle name="Normal_#10-Headcount" xfId="7"/>
+    <cellStyle name="標準_(D)日程計画" xfId="8"/>
+    <cellStyle name="表示済みのハイパーリンク_02_1st_2ndOTP対応機能一覧_一応完成版" xfId="9"/>
+    <cellStyle name="常规_GM09MR_RTM_DisplayAPP_Sub_C" xfId="10"/>
+    <cellStyle name="常规_Sheet4" xfId="11"/>
+    <cellStyle name="常规_需求跟踪矩阵" xfId="12"/>
+    <cellStyle name="常规_需求跟踪矩阵模板" xfId="13"/>
+    <cellStyle name="段落标题1" xfId="14"/>
+    <cellStyle name="段落标题2" xfId="15"/>
+    <cellStyle name="桁区切り [0.00]_(D)日程計画" xfId="16"/>
+    <cellStyle name="桁区切り_(D)日程計画" xfId="17"/>
+    <cellStyle name="普通_laroux" xfId="18"/>
+    <cellStyle name="千位[0]_laroux" xfId="19"/>
+    <cellStyle name="千位_laroux" xfId="20"/>
+    <cellStyle name="通貨 [0.00]_(D)日程計画" xfId="21"/>
+    <cellStyle name="通貨_(D)日程計画" xfId="22"/>
+    <cellStyle name="样式 1" xfId="23"/>
+    <cellStyle name="표준_Book1" xfId="24"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor indexed="22"/>
+          <bgColor indexed="23"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor indexed="23"/>
+          <bgColor indexed="22"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3279,6 +2685,7 @@
       <a:lstStyle/>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -3289,391 +2696,392 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.75" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="15"/>
   <cols>
-    <col width="9.875" customWidth="1" style="138" min="1" max="1"/>
-    <col width="10.375" customWidth="1" style="138" min="2" max="2"/>
-    <col width="9.875" customWidth="1" style="138" min="3" max="3"/>
-    <col width="8.75" customWidth="1" style="138" min="4" max="4"/>
-    <col width="10" customWidth="1" style="138" min="5" max="5"/>
-    <col width="9.75" customWidth="1" style="138" min="6" max="6"/>
-    <col width="9.5" customWidth="1" style="138" min="7" max="7"/>
-    <col width="16.75" customWidth="1" style="138" min="8" max="8"/>
-    <col width="8.75" customWidth="1" style="138" min="9" max="16384"/>
+    <col width="9.90625" customWidth="1" style="134" min="1" max="1"/>
+    <col width="10.36328125" customWidth="1" style="134" min="2" max="2"/>
+    <col width="9.90625" customWidth="1" style="134" min="3" max="3"/>
+    <col width="8.7265625" customWidth="1" style="134" min="4" max="4"/>
+    <col width="10" customWidth="1" style="134" min="5" max="5"/>
+    <col width="9.7265625" customWidth="1" style="134" min="6" max="6"/>
+    <col width="9.453125" customWidth="1" style="134" min="7" max="7"/>
+    <col width="16.7265625" customWidth="1" style="134" min="8" max="8"/>
+    <col width="8.7265625" customWidth="1" style="134" min="9" max="9"/>
+    <col width="8.7265625" customWidth="1" style="134" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="139" t="n"/>
+      <c r="A1" s="135" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="139" t="n"/>
-    </row>
-    <row r="3" ht="23.25" customFormat="1" customHeight="1" s="137">
-      <c r="A3" s="140" t="inlineStr">
+      <c r="A2" s="135" t="n"/>
+    </row>
+    <row r="3" ht="23.25" customFormat="1" customHeight="1" s="154">
+      <c r="A3" s="136" t="inlineStr">
         <is>
           <t>密级：</t>
         </is>
       </c>
-      <c r="B3" s="141" t="inlineStr">
+      <c r="B3" s="137" t="inlineStr">
         <is>
           <t>机密</t>
         </is>
       </c>
-      <c r="C3" s="142" t="n"/>
-      <c r="D3" s="142" t="n"/>
-      <c r="E3" s="142" t="n"/>
-      <c r="F3" s="142" t="n"/>
-      <c r="G3" s="142" t="n"/>
-      <c r="H3" s="143" t="n"/>
-    </row>
-    <row r="4" ht="23.25" customFormat="1" customHeight="1" s="137">
-      <c r="A4" s="144" t="n"/>
-      <c r="H4" s="145" t="inlineStr">
+      <c r="C3" s="138" t="n"/>
+      <c r="D3" s="138" t="n"/>
+      <c r="E3" s="138" t="n"/>
+      <c r="F3" s="138" t="n"/>
+      <c r="G3" s="138" t="n"/>
+      <c r="H3" s="139" t="n"/>
+    </row>
+    <row r="4" ht="23.25" customFormat="1" customHeight="1" s="154">
+      <c r="A4" s="156" t="n"/>
+      <c r="H4" s="140" t="inlineStr">
         <is>
           <t>第   版</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="23.25" customFormat="1" customHeight="1" s="137">
-      <c r="A5" s="144" t="inlineStr">
+    <row r="5" ht="23.25" customFormat="1" customHeight="1" s="154">
+      <c r="A5" s="156" t="inlineStr">
         <is>
           <t>分册名称：无</t>
         </is>
       </c>
-      <c r="F5" s="142" t="n"/>
-      <c r="G5" s="146" t="inlineStr">
+      <c r="F5" s="138" t="n"/>
+      <c r="G5" s="157" t="inlineStr">
         <is>
           <t>第 1 册/共 1 册</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="147" t="n"/>
-      <c r="B6" s="148" t="n"/>
-      <c r="C6" s="148" t="n"/>
-      <c r="D6" s="148" t="n"/>
-      <c r="E6" s="148" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A7" s="149" t="n"/>
-      <c r="B7" s="143" t="n"/>
-      <c r="C7" s="143" t="n"/>
-      <c r="D7" s="143" t="n"/>
-      <c r="E7" s="143" t="n"/>
-      <c r="F7" s="143" t="n"/>
-      <c r="G7" s="143" t="n"/>
-      <c r="H7" s="143" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A8" s="149" t="n"/>
-      <c r="B8" s="143" t="n"/>
-      <c r="C8" s="143" t="n"/>
-      <c r="D8" s="143" t="n"/>
-      <c r="E8" s="143" t="n"/>
-      <c r="F8" s="143" t="n"/>
-      <c r="G8" s="143" t="n"/>
-      <c r="H8" s="143" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A9" s="149" t="n"/>
-      <c r="B9" s="143" t="n"/>
-      <c r="C9" s="143" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="143" t="n"/>
-      <c r="F9" s="143" t="n"/>
-      <c r="G9" s="143" t="n"/>
-      <c r="H9" s="143" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A10" s="149" t="n"/>
-      <c r="B10" s="143" t="n"/>
-      <c r="C10" s="143" t="n"/>
-      <c r="D10" s="143" t="n"/>
-      <c r="E10" s="143" t="n"/>
-      <c r="F10" s="143" t="n"/>
-      <c r="G10" s="143" t="n"/>
-      <c r="H10" s="143" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A11" s="149" t="n"/>
-      <c r="B11" s="143" t="n"/>
-      <c r="C11" s="143" t="n"/>
-      <c r="D11" s="143" t="n"/>
-      <c r="E11" s="143" t="n"/>
-      <c r="F11" s="143" t="n"/>
-      <c r="G11" s="143" t="n"/>
-      <c r="H11" s="143" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A12" s="149" t="n"/>
-      <c r="B12" s="143" t="n"/>
-      <c r="C12" s="143" t="n"/>
-      <c r="D12" s="143" t="n"/>
-      <c r="E12" s="143" t="n"/>
-      <c r="F12" s="143" t="n"/>
-      <c r="G12" s="143" t="n"/>
-      <c r="H12" s="143" t="n"/>
-    </row>
-    <row r="13" ht="46.5" customFormat="1" customHeight="1" s="137">
-      <c r="A13" s="150" t="inlineStr">
+      <c r="A6" s="141" t="n"/>
+      <c r="B6" s="142" t="n"/>
+      <c r="C6" s="142" t="n"/>
+      <c r="D6" s="142" t="n"/>
+      <c r="E6" s="142" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A7" s="143" t="n"/>
+      <c r="B7" s="139" t="n"/>
+      <c r="C7" s="139" t="n"/>
+      <c r="D7" s="139" t="n"/>
+      <c r="E7" s="139" t="n"/>
+      <c r="F7" s="139" t="n"/>
+      <c r="G7" s="139" t="n"/>
+      <c r="H7" s="139" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A8" s="143" t="n"/>
+      <c r="B8" s="139" t="n"/>
+      <c r="C8" s="139" t="n"/>
+      <c r="D8" s="139" t="n"/>
+      <c r="E8" s="139" t="n"/>
+      <c r="F8" s="139" t="n"/>
+      <c r="G8" s="139" t="n"/>
+      <c r="H8" s="139" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A9" s="143" t="n"/>
+      <c r="B9" s="139" t="n"/>
+      <c r="C9" s="139" t="n"/>
+      <c r="D9" s="139" t="n"/>
+      <c r="E9" s="139" t="n"/>
+      <c r="F9" s="139" t="n"/>
+      <c r="G9" s="139" t="n"/>
+      <c r="H9" s="139" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A10" s="143" t="n"/>
+      <c r="B10" s="139" t="n"/>
+      <c r="C10" s="139" t="n"/>
+      <c r="D10" s="139" t="n"/>
+      <c r="E10" s="139" t="n"/>
+      <c r="F10" s="139" t="n"/>
+      <c r="G10" s="139" t="n"/>
+      <c r="H10" s="139" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A11" s="143" t="n"/>
+      <c r="B11" s="139" t="n"/>
+      <c r="C11" s="139" t="n"/>
+      <c r="D11" s="139" t="n"/>
+      <c r="E11" s="139" t="n"/>
+      <c r="F11" s="139" t="n"/>
+      <c r="G11" s="139" t="n"/>
+      <c r="H11" s="139" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A12" s="143" t="n"/>
+      <c r="B12" s="139" t="n"/>
+      <c r="C12" s="139" t="n"/>
+      <c r="D12" s="139" t="n"/>
+      <c r="E12" s="139" t="n"/>
+      <c r="F12" s="139" t="n"/>
+      <c r="G12" s="139" t="n"/>
+      <c r="H12" s="139" t="n"/>
+    </row>
+    <row r="13" ht="46.5" customFormat="1" customHeight="1" s="154">
+      <c r="A13" s="158" t="inlineStr">
         <is>
           <t>项目名</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A14" s="149" t="n"/>
-      <c r="B14" s="151" t="n"/>
-      <c r="C14" s="143" t="n"/>
-      <c r="D14" s="143" t="n"/>
-      <c r="E14" s="143" t="n"/>
-      <c r="F14" s="143" t="n"/>
-      <c r="G14" s="143" t="n"/>
-      <c r="H14" s="143" t="n"/>
-    </row>
-    <row r="15" ht="46.5" customFormat="1" customHeight="1" s="137">
-      <c r="A15" s="152" t="inlineStr">
+    <row r="14" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A14" s="143" t="n"/>
+      <c r="B14" s="144" t="n"/>
+      <c r="C14" s="139" t="n"/>
+      <c r="D14" s="139" t="n"/>
+      <c r="E14" s="139" t="n"/>
+      <c r="F14" s="139" t="n"/>
+      <c r="G14" s="139" t="n"/>
+      <c r="H14" s="139" t="n"/>
+    </row>
+    <row r="15" ht="46.5" customFormat="1" customHeight="1" s="154">
+      <c r="A15" s="153" t="inlineStr">
         <is>
           <t>需求跟踪矩阵</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A16" s="149" t="n"/>
-      <c r="B16" s="143" t="n"/>
-      <c r="C16" s="143" t="n"/>
-      <c r="D16" s="143" t="n"/>
-      <c r="E16" s="143" t="n"/>
-      <c r="F16" s="143" t="n"/>
-      <c r="G16" s="143" t="n"/>
-      <c r="H16" s="143" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A17" s="149" t="n"/>
-      <c r="B17" s="143" t="n"/>
-      <c r="C17" s="143" t="n"/>
-      <c r="D17" s="143" t="n"/>
-      <c r="E17" s="143" t="n"/>
-      <c r="F17" s="143" t="n"/>
-      <c r="G17" s="143" t="n"/>
-      <c r="H17" s="143" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A18" s="149" t="n"/>
-      <c r="B18" s="143" t="n"/>
-      <c r="C18" s="143" t="n"/>
-      <c r="D18" s="143" t="n"/>
-      <c r="E18" s="143" t="n"/>
-      <c r="F18" s="143" t="n"/>
-      <c r="G18" s="143" t="n"/>
-      <c r="H18" s="143" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A19" s="149" t="n"/>
-      <c r="B19" s="143" t="n"/>
-      <c r="C19" s="143" t="n"/>
-      <c r="D19" s="143" t="n"/>
-      <c r="E19" s="143" t="n"/>
-      <c r="F19" s="143" t="n"/>
-      <c r="G19" s="143" t="n"/>
-      <c r="H19" s="143" t="n"/>
-    </row>
-    <row r="20" ht="22.5" customFormat="1" customHeight="1" s="137">
-      <c r="A20" s="153" t="inlineStr">
+    <row r="16" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A16" s="143" t="n"/>
+      <c r="B16" s="139" t="n"/>
+      <c r="C16" s="139" t="n"/>
+      <c r="D16" s="139" t="n"/>
+      <c r="E16" s="139" t="n"/>
+      <c r="F16" s="139" t="n"/>
+      <c r="G16" s="139" t="n"/>
+      <c r="H16" s="139" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A17" s="143" t="n"/>
+      <c r="B17" s="139" t="n"/>
+      <c r="C17" s="139" t="n"/>
+      <c r="D17" s="139" t="n"/>
+      <c r="E17" s="139" t="n"/>
+      <c r="F17" s="139" t="n"/>
+      <c r="G17" s="139" t="n"/>
+      <c r="H17" s="139" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A18" s="143" t="n"/>
+      <c r="B18" s="139" t="n"/>
+      <c r="C18" s="139" t="n"/>
+      <c r="D18" s="139" t="n"/>
+      <c r="E18" s="139" t="n"/>
+      <c r="F18" s="139" t="n"/>
+      <c r="G18" s="139" t="n"/>
+      <c r="H18" s="139" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A19" s="143" t="n"/>
+      <c r="B19" s="139" t="n"/>
+      <c r="C19" s="139" t="n"/>
+      <c r="D19" s="139" t="n"/>
+      <c r="E19" s="139" t="n"/>
+      <c r="F19" s="139" t="n"/>
+      <c r="G19" s="139" t="n"/>
+      <c r="H19" s="139" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customFormat="1" customHeight="1" s="154">
+      <c r="A20" s="155" t="inlineStr">
         <is>
           <t>实习实训中心</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A21" s="149" t="n"/>
-      <c r="B21" s="143" t="n"/>
-      <c r="C21" s="143" t="n"/>
-      <c r="D21" s="143" t="n"/>
-      <c r="E21" s="143" t="n"/>
-      <c r="F21" s="143" t="n"/>
-      <c r="G21" s="143" t="n"/>
-      <c r="H21" s="143" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A22" s="149" t="n"/>
-      <c r="B22" s="143" t="n"/>
-      <c r="C22" s="143" t="n"/>
-      <c r="D22" s="143" t="n"/>
-      <c r="E22" s="143" t="n"/>
-      <c r="F22" s="143" t="n"/>
-      <c r="G22" s="143" t="n"/>
-      <c r="H22" s="143" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A23" s="149" t="n"/>
-      <c r="B23" s="143" t="n"/>
-      <c r="C23" s="143" t="n"/>
-      <c r="D23" s="143" t="n"/>
-      <c r="E23" s="143" t="n"/>
-      <c r="F23" s="143" t="n"/>
-      <c r="G23" s="143" t="n"/>
-      <c r="H23" s="143" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A24" s="149" t="n"/>
-      <c r="B24" s="143" t="n"/>
-      <c r="C24" s="143" t="n"/>
-      <c r="D24" s="143" t="n"/>
-      <c r="E24" s="143" t="n"/>
-      <c r="F24" s="143" t="n"/>
-      <c r="G24" s="143" t="n"/>
-      <c r="H24" s="143" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A25" s="149" t="n"/>
-      <c r="B25" s="143" t="n"/>
-      <c r="C25" s="143" t="n"/>
-      <c r="D25" s="143" t="n"/>
-      <c r="E25" s="143" t="n"/>
-      <c r="F25" s="143" t="n"/>
-      <c r="G25" s="143" t="n"/>
-      <c r="H25" s="143" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A26" s="149" t="n"/>
-      <c r="B26" s="143" t="n"/>
-      <c r="C26" s="143" t="n"/>
-      <c r="D26" s="143" t="n"/>
-      <c r="E26" s="143" t="n"/>
-      <c r="F26" s="143" t="n"/>
-      <c r="G26" s="143" t="n"/>
-      <c r="H26" s="143" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A27" s="149" t="n"/>
-      <c r="B27" s="143" t="n"/>
-      <c r="C27" s="143" t="n"/>
-      <c r="D27" s="143" t="n"/>
-      <c r="E27" s="143" t="n"/>
-      <c r="F27" s="143" t="n"/>
-      <c r="G27" s="143" t="n"/>
-      <c r="H27" s="143" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A28" s="149" t="n"/>
-      <c r="B28" s="143" t="n"/>
-      <c r="C28" s="143" t="n"/>
-      <c r="D28" s="143" t="n"/>
-      <c r="E28" s="143" t="n"/>
-      <c r="F28" s="143" t="n"/>
-      <c r="G28" s="143" t="n"/>
-      <c r="H28" s="143" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A29" s="149" t="n"/>
-      <c r="B29" s="143" t="n"/>
-      <c r="C29" s="143" t="n"/>
-      <c r="D29" s="143" t="n"/>
-      <c r="E29" s="143" t="n"/>
-      <c r="F29" s="143" t="n"/>
-      <c r="G29" s="143" t="n"/>
-      <c r="H29" s="143" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A30" s="149" t="n"/>
-      <c r="B30" s="143" t="n"/>
-      <c r="C30" s="143" t="n"/>
-      <c r="D30" s="143" t="n"/>
-      <c r="E30" s="143" t="n"/>
-      <c r="F30" s="143" t="n"/>
-      <c r="G30" s="143" t="n"/>
-      <c r="H30" s="143" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A31" s="149" t="n"/>
-      <c r="B31" s="143" t="n"/>
-      <c r="C31" s="143" t="n"/>
-      <c r="D31" s="143" t="n"/>
-      <c r="E31" s="143" t="n"/>
-      <c r="F31" s="143" t="n"/>
-      <c r="G31" s="143" t="n"/>
-      <c r="H31" s="143" t="n"/>
-    </row>
-    <row r="32" ht="22.5" customFormat="1" customHeight="1" s="137">
-      <c r="A32" s="154" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A33" s="149" t="n"/>
-      <c r="B33" s="143" t="n"/>
-      <c r="C33" s="143" t="n"/>
-      <c r="D33" s="143" t="n"/>
-      <c r="E33" s="143" t="n"/>
-      <c r="F33" s="143" t="n"/>
-      <c r="G33" s="143" t="n"/>
-      <c r="H33" s="143" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A34" s="149" t="n"/>
-      <c r="B34" s="143" t="n"/>
-      <c r="C34" s="143" t="n"/>
-      <c r="D34" s="143" t="n"/>
-      <c r="E34" s="143" t="n"/>
-      <c r="F34" s="143" t="n"/>
-      <c r="G34" s="143" t="n"/>
-      <c r="H34" s="143" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A35" s="149" t="n"/>
-      <c r="B35" s="143" t="n"/>
-      <c r="C35" s="143" t="n"/>
-      <c r="D35" s="143" t="n"/>
-      <c r="E35" s="143" t="n"/>
-      <c r="F35" s="143" t="n"/>
-      <c r="G35" s="143" t="n"/>
-      <c r="H35" s="143" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customFormat="1" customHeight="1" s="137">
-      <c r="A36" s="155" t="inlineStr">
+    <row r="21" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A21" s="143" t="n"/>
+      <c r="B21" s="139" t="n"/>
+      <c r="C21" s="139" t="n"/>
+      <c r="D21" s="139" t="n"/>
+      <c r="E21" s="139" t="n"/>
+      <c r="F21" s="139" t="n"/>
+      <c r="G21" s="139" t="n"/>
+      <c r="H21" s="139" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A22" s="143" t="n"/>
+      <c r="B22" s="139" t="n"/>
+      <c r="C22" s="139" t="n"/>
+      <c r="D22" s="139" t="n"/>
+      <c r="E22" s="139" t="n"/>
+      <c r="F22" s="139" t="n"/>
+      <c r="G22" s="139" t="n"/>
+      <c r="H22" s="139" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A23" s="143" t="n"/>
+      <c r="B23" s="139" t="n"/>
+      <c r="C23" s="139" t="n"/>
+      <c r="D23" s="139" t="n"/>
+      <c r="E23" s="139" t="n"/>
+      <c r="F23" s="139" t="n"/>
+      <c r="G23" s="139" t="n"/>
+      <c r="H23" s="139" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A24" s="143" t="n"/>
+      <c r="B24" s="139" t="n"/>
+      <c r="C24" s="139" t="n"/>
+      <c r="D24" s="139" t="n"/>
+      <c r="E24" s="139" t="n"/>
+      <c r="F24" s="139" t="n"/>
+      <c r="G24" s="139" t="n"/>
+      <c r="H24" s="139" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A25" s="143" t="n"/>
+      <c r="B25" s="139" t="n"/>
+      <c r="C25" s="139" t="n"/>
+      <c r="D25" s="139" t="n"/>
+      <c r="E25" s="139" t="n"/>
+      <c r="F25" s="139" t="n"/>
+      <c r="G25" s="139" t="n"/>
+      <c r="H25" s="139" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A26" s="143" t="n"/>
+      <c r="B26" s="139" t="n"/>
+      <c r="C26" s="139" t="n"/>
+      <c r="D26" s="139" t="n"/>
+      <c r="E26" s="139" t="n"/>
+      <c r="F26" s="139" t="n"/>
+      <c r="G26" s="139" t="n"/>
+      <c r="H26" s="139" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A27" s="143" t="n"/>
+      <c r="B27" s="139" t="n"/>
+      <c r="C27" s="139" t="n"/>
+      <c r="D27" s="139" t="n"/>
+      <c r="E27" s="139" t="n"/>
+      <c r="F27" s="139" t="n"/>
+      <c r="G27" s="139" t="n"/>
+      <c r="H27" s="139" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A28" s="143" t="n"/>
+      <c r="B28" s="139" t="n"/>
+      <c r="C28" s="139" t="n"/>
+      <c r="D28" s="139" t="n"/>
+      <c r="E28" s="139" t="n"/>
+      <c r="F28" s="139" t="n"/>
+      <c r="G28" s="139" t="n"/>
+      <c r="H28" s="139" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A29" s="143" t="n"/>
+      <c r="B29" s="139" t="n"/>
+      <c r="C29" s="139" t="n"/>
+      <c r="D29" s="139" t="n"/>
+      <c r="E29" s="139" t="n"/>
+      <c r="F29" s="139" t="n"/>
+      <c r="G29" s="139" t="n"/>
+      <c r="H29" s="139" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A30" s="143" t="n"/>
+      <c r="B30" s="139" t="n"/>
+      <c r="C30" s="139" t="n"/>
+      <c r="D30" s="139" t="n"/>
+      <c r="E30" s="139" t="n"/>
+      <c r="F30" s="139" t="n"/>
+      <c r="G30" s="139" t="n"/>
+      <c r="H30" s="139" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A31" s="143" t="n"/>
+      <c r="B31" s="139" t="n"/>
+      <c r="C31" s="139" t="n"/>
+      <c r="D31" s="139" t="n"/>
+      <c r="E31" s="139" t="n"/>
+      <c r="F31" s="139" t="n"/>
+      <c r="G31" s="139" t="n"/>
+      <c r="H31" s="139" t="n"/>
+    </row>
+    <row r="32" ht="22.5" customFormat="1" customHeight="1" s="154">
+      <c r="A32" s="159" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A33" s="143" t="n"/>
+      <c r="B33" s="139" t="n"/>
+      <c r="C33" s="139" t="n"/>
+      <c r="D33" s="139" t="n"/>
+      <c r="E33" s="139" t="n"/>
+      <c r="F33" s="139" t="n"/>
+      <c r="G33" s="139" t="n"/>
+      <c r="H33" s="139" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A34" s="143" t="n"/>
+      <c r="B34" s="139" t="n"/>
+      <c r="C34" s="139" t="n"/>
+      <c r="D34" s="139" t="n"/>
+      <c r="E34" s="139" t="n"/>
+      <c r="F34" s="139" t="n"/>
+      <c r="G34" s="139" t="n"/>
+      <c r="H34" s="139" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A35" s="143" t="n"/>
+      <c r="B35" s="139" t="n"/>
+      <c r="C35" s="139" t="n"/>
+      <c r="D35" s="139" t="n"/>
+      <c r="E35" s="139" t="n"/>
+      <c r="F35" s="139" t="n"/>
+      <c r="G35" s="139" t="n"/>
+      <c r="H35" s="139" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customFormat="1" customHeight="1" s="154">
+      <c r="A36" s="145" t="inlineStr">
         <is>
           <t>总页数</t>
         </is>
       </c>
-      <c r="B36" s="156" t="n"/>
-      <c r="C36" s="155" t="inlineStr">
+      <c r="B36" s="146" t="n"/>
+      <c r="C36" s="145" t="inlineStr">
         <is>
           <t>正文</t>
         </is>
       </c>
-      <c r="D36" s="156" t="n"/>
-      <c r="E36" s="155" t="inlineStr">
+      <c r="D36" s="146" t="n"/>
+      <c r="E36" s="145" t="inlineStr">
         <is>
           <t>附录</t>
         </is>
       </c>
-      <c r="F36" s="157" t="n"/>
-      <c r="G36" s="155" t="inlineStr">
+      <c r="F36" s="147" t="n"/>
+      <c r="G36" s="145" t="inlineStr">
         <is>
           <t>生效日期</t>
         </is>
       </c>
-      <c r="H36" s="158" t="n"/>
-    </row>
-    <row r="37" ht="14.25" customFormat="1" customHeight="1" s="137">
-      <c r="A37" s="159" t="inlineStr">
+      <c r="H36" s="148" t="n"/>
+    </row>
+    <row r="37" ht="14.25" customFormat="1" customHeight="1" s="154">
+      <c r="A37" s="149" t="inlineStr">
         <is>
           <t>编制：</t>
         </is>
       </c>
-      <c r="B37" s="160" t="n"/>
-      <c r="C37" s="161" t="n"/>
-      <c r="D37" s="162" t="n"/>
-      <c r="E37" s="159" t="inlineStr">
+      <c r="B37" s="150" t="n"/>
+      <c r="C37" s="151" t="n"/>
+      <c r="D37" s="152" t="n"/>
+      <c r="E37" s="149" t="inlineStr">
         <is>
           <t>审批：</t>
         </is>
       </c>
-      <c r="F37" s="163" t="n"/>
-      <c r="G37" s="161" t="n"/>
-      <c r="H37" s="162" t="n"/>
+      <c r="F37" s="160" t="n"/>
+      <c r="G37" s="151" t="n"/>
+      <c r="H37" s="152" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="139" t="n"/>
+      <c r="A38" s="135" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3699,586 +3107,633 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:P23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="0.875" customWidth="1" style="84" min="1" max="1"/>
-    <col width="3.375" customWidth="1" style="84" min="2" max="2"/>
-    <col width="10.75" customWidth="1" style="85" min="3" max="3"/>
-    <col width="23.375" customWidth="1" style="84" min="4" max="4"/>
-    <col width="7.375" customWidth="1" style="84" min="5" max="5"/>
-    <col width="12.75" customWidth="1" style="84" min="6" max="6"/>
-    <col width="9.375" customWidth="1" style="84" min="7" max="7"/>
-    <col width="6.875" customWidth="1" style="84" min="8" max="8"/>
-    <col width="6.875" customWidth="1" style="83" min="9" max="10"/>
-    <col width="6.875" customWidth="1" style="84" min="11" max="13"/>
-    <col width="12" customWidth="1" style="84" min="14" max="16"/>
-    <col width="9" customWidth="1" style="84" min="17" max="16384"/>
+    <col width="0.90625" customWidth="1" style="80" min="1" max="1"/>
+    <col width="3.36328125" customWidth="1" style="80" min="2" max="2"/>
+    <col width="10.7265625" customWidth="1" style="81" min="3" max="3"/>
+    <col width="23.36328125" customWidth="1" style="80" min="4" max="4"/>
+    <col width="7.36328125" customWidth="1" style="80" min="5" max="5"/>
+    <col width="12.7265625" customWidth="1" style="80" min="6" max="6"/>
+    <col width="9.36328125" customWidth="1" style="80" min="7" max="7"/>
+    <col width="6.90625" customWidth="1" style="80" min="8" max="8"/>
+    <col width="6.90625" customWidth="1" style="79" min="9" max="10"/>
+    <col width="6.90625" customWidth="1" style="80" min="11" max="13"/>
+    <col width="12" customWidth="1" style="80" min="14" max="16"/>
+    <col width="9" customWidth="1" style="80" min="17" max="17"/>
+    <col width="9" customWidth="1" style="80" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.25" customFormat="1" customHeight="1" s="78">
-      <c r="B1" s="86" t="inlineStr">
+    <row r="1" ht="29.25" customFormat="1" customHeight="1" s="74">
+      <c r="B1" s="82" t="inlineStr">
         <is>
           <t>变更履历</t>
         </is>
       </c>
-      <c r="C1" s="87" t="n"/>
-      <c r="D1" s="87" t="n"/>
-      <c r="E1" s="87" t="n"/>
-      <c r="F1" s="87" t="n"/>
-      <c r="G1" s="87" t="n"/>
-      <c r="H1" s="87" t="n"/>
-      <c r="I1" s="88" t="n"/>
-      <c r="J1" s="88" t="n"/>
-      <c r="K1" s="87" t="n"/>
-      <c r="L1" s="88" t="n"/>
-      <c r="M1" s="87" t="n"/>
-      <c r="N1" s="87" t="n"/>
-      <c r="O1" s="87" t="n"/>
-      <c r="P1" s="87" t="n"/>
-    </row>
-    <row r="2" ht="24.75" customFormat="1" customHeight="1" s="79">
-      <c r="B2" s="89" t="inlineStr">
+      <c r="C1" s="83" t="n"/>
+      <c r="D1" s="83" t="n"/>
+      <c r="E1" s="83" t="n"/>
+      <c r="F1" s="83" t="n"/>
+      <c r="G1" s="83" t="n"/>
+      <c r="H1" s="83" t="n"/>
+      <c r="I1" s="84" t="n"/>
+      <c r="J1" s="84" t="n"/>
+      <c r="K1" s="83" t="n"/>
+      <c r="L1" s="84" t="n"/>
+      <c r="M1" s="83" t="n"/>
+      <c r="N1" s="83" t="n"/>
+      <c r="O1" s="83" t="n"/>
+      <c r="P1" s="83" t="n"/>
+    </row>
+    <row r="2" ht="24.75" customFormat="1" customHeight="1" s="75">
+      <c r="B2" s="85" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C2" s="90" t="inlineStr">
+      <c r="C2" s="86" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D2" s="90" t="inlineStr">
+      <c r="D2" s="86" t="inlineStr">
         <is>
           <t>变更内容</t>
         </is>
       </c>
-      <c r="E2" s="90" t="inlineStr">
+      <c r="E2" s="86" t="inlineStr">
         <is>
           <t>RTM No.</t>
         </is>
       </c>
-      <c r="F2" s="90" t="inlineStr">
+      <c r="F2" s="86" t="inlineStr">
         <is>
           <t>需求版本</t>
         </is>
       </c>
-      <c r="G2" s="90" t="inlineStr">
+      <c r="G2" s="86" t="inlineStr">
         <is>
           <t>变更人</t>
         </is>
       </c>
-      <c r="H2" s="90" t="inlineStr">
+      <c r="H2" s="86" t="inlineStr">
         <is>
           <t>初始需求个数</t>
         </is>
       </c>
-      <c r="I2" s="90" t="inlineStr">
+      <c r="I2" s="86" t="inlineStr">
         <is>
           <t>新增需求个数</t>
         </is>
       </c>
-      <c r="J2" s="90" t="inlineStr">
+      <c r="J2" s="86" t="inlineStr">
         <is>
           <t>删除需求个数</t>
         </is>
       </c>
-      <c r="K2" s="90" t="inlineStr">
+      <c r="K2" s="86" t="inlineStr">
         <is>
           <t>修改需求个数</t>
         </is>
       </c>
-      <c r="L2" s="90" t="inlineStr">
+      <c r="L2" s="86" t="inlineStr">
         <is>
           <t>总需求个数</t>
         </is>
       </c>
-      <c r="M2" s="90" t="inlineStr">
+      <c r="M2" s="86" t="inlineStr">
         <is>
           <t>需求变更比</t>
         </is>
       </c>
-      <c r="N2" s="90" t="inlineStr">
+      <c r="N2" s="86" t="inlineStr">
         <is>
           <t>对规模的影响</t>
         </is>
       </c>
-      <c r="O2" s="90" t="inlineStr">
+      <c r="O2" s="86" t="inlineStr">
         <is>
           <t>对工作量的影响</t>
         </is>
       </c>
-      <c r="P2" s="91" t="inlineStr">
+      <c r="P2" s="87" t="inlineStr">
         <is>
           <t>对进度的影响</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customFormat="1" customHeight="1" s="80">
-      <c r="B3" s="92" t="inlineStr">
+    <row r="3" ht="13.5" customFormat="1" customHeight="1" s="76">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C3" s="164" t="inlineStr">
+      <c r="C3" s="168" t="inlineStr">
         <is>
           <t>首次编制：按老师模板（旧衣回收碳减排追踪与积分商城系统·需求跟踪矩阵）格式，将需求分析说明书功能需求整理为 42 条 RTM，按 大分類/中分類/小分類 归类，图号=原型评审图号</t>
         </is>
       </c>
-      <c r="D3" s="94" t="inlineStr">
+      <c r="D3" s="90" t="inlineStr">
         <is>
           <t>设计用RTM</t>
         </is>
       </c>
-      <c r="E3" s="95" t="inlineStr">
+      <c r="E3" s="91" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="F3" s="96" t="inlineStr">
+      <c r="F3" s="92" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
-      <c r="G3" s="97" t="inlineStr">
+      <c r="G3" s="93" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H3" s="96" t="inlineStr">
+      <c r="H3" s="92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" s="96" t="inlineStr">
+      <c r="I3" s="92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="96" t="inlineStr">
+      <c r="J3" s="92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K3" s="96" t="inlineStr">
+      <c r="K3" s="92" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="L3" s="98" t="inlineStr">
+      <c r="L3" s="94" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="M3" s="165" t="inlineStr">
+      <c r="M3" s="169" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="N3" s="97" t="inlineStr">
+      <c r="N3" s="93" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="O3" s="97" t="inlineStr">
+      <c r="O3" s="93" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="P3" s="100" t="n"/>
-    </row>
-    <row r="4" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B4" s="101" t="inlineStr">
+      <c r="P3" s="96" t="n"/>
+    </row>
+    <row r="4" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C4" s="166" t="inlineStr">
+      <c r="C4" s="170" t="inlineStr">
         <is>
           <t>补充任务分工：丘宇乾(COD 后端), 梁霁鸣(PD 原型/老人端/家属端 RTM), 周彦龙(UT 护工端/管理员 RTM+ 测试)</t>
         </is>
       </c>
-      <c r="D4" s="103" t="inlineStr">
+      <c r="D4" s="99" t="inlineStr">
         <is>
           <t>设计用RTM</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="100" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
       </c>
-      <c r="F4" s="105" t="inlineStr">
+      <c r="F4" s="101" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="G4" s="106" t="n">
+      <c r="G4" s="102" t="n">
         <v>42</v>
       </c>
-      <c r="H4" s="107" t="n">
+      <c r="H4" s="103" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="105" t="n">
+      <c r="I4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="105" t="n">
+      <c r="J4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="105" t="n">
+      <c r="K4" s="101" t="n">
         <v>42</v>
       </c>
-      <c r="L4" s="108" t="inlineStr">
+      <c r="L4" s="104" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="M4" s="167" t="inlineStr">
+      <c r="M4" s="171" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="N4" s="106" t="inlineStr">
+      <c r="N4" s="102" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="O4" s="106" t="inlineStr">
+      <c r="O4" s="102" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="P4" s="110" t="n"/>
-    </row>
-    <row r="5" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B5" s="101" t="n"/>
-      <c r="C5" s="166" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="104" t="n"/>
-      <c r="F5" s="105" t="n"/>
-      <c r="G5" s="106" t="n"/>
-      <c r="H5" s="107" t="n"/>
-      <c r="I5" s="105" t="n"/>
-      <c r="J5" s="105" t="n"/>
-      <c r="K5" s="105" t="n"/>
-      <c r="L5" s="108" t="n"/>
-      <c r="M5" s="167" t="n"/>
-      <c r="N5" s="106" t="n"/>
-      <c r="O5" s="106" t="n"/>
-      <c r="P5" s="110" t="n"/>
-    </row>
-    <row r="6" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B6" s="101" t="n"/>
-      <c r="C6" s="166" t="n"/>
-      <c r="D6" s="103" t="n"/>
-      <c r="E6" s="104" t="n"/>
-      <c r="F6" s="105" t="n"/>
-      <c r="G6" s="106" t="n"/>
-      <c r="H6" s="107" t="n"/>
-      <c r="I6" s="105" t="n"/>
-      <c r="J6" s="105" t="n"/>
-      <c r="K6" s="105" t="n"/>
-      <c r="L6" s="108" t="n"/>
-      <c r="M6" s="167" t="n"/>
-      <c r="N6" s="106" t="n"/>
-      <c r="O6" s="106" t="n"/>
-      <c r="P6" s="110" t="n"/>
-    </row>
-    <row r="7" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B7" s="101" t="n"/>
-      <c r="C7" s="166" t="n"/>
-      <c r="D7" s="103" t="n"/>
-      <c r="E7" s="104" t="n"/>
-      <c r="F7" s="105" t="n"/>
-      <c r="G7" s="106" t="n"/>
-      <c r="H7" s="107" t="n"/>
-      <c r="I7" s="105" t="n"/>
-      <c r="J7" s="105" t="n"/>
-      <c r="K7" s="105" t="n"/>
-      <c r="L7" s="108" t="n"/>
-      <c r="M7" s="167" t="n"/>
-      <c r="N7" s="105" t="n"/>
-      <c r="O7" s="106" t="n"/>
-      <c r="P7" s="110" t="n"/>
-    </row>
-    <row r="8" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B8" s="101" t="n"/>
-      <c r="C8" s="166" t="n"/>
-      <c r="D8" s="103" t="n"/>
-      <c r="E8" s="104" t="n"/>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="106" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="105" t="n"/>
-      <c r="J8" s="105" t="n"/>
-      <c r="K8" s="105" t="n"/>
-      <c r="L8" s="108" t="n"/>
-      <c r="M8" s="167" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="110" t="n"/>
-    </row>
-    <row r="9" ht="12" customFormat="1" customHeight="1" s="81">
-      <c r="B9" s="111" t="n"/>
-      <c r="C9" s="168" t="n"/>
-      <c r="D9" s="113" t="n"/>
-      <c r="E9" s="114" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="116" t="n"/>
-      <c r="H9" s="117" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="108" t="n"/>
-      <c r="M9" s="167" t="n"/>
-      <c r="N9" s="115" t="n"/>
-      <c r="O9" s="115" t="n"/>
-      <c r="P9" s="118" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B10" s="101" t="n"/>
-      <c r="C10" s="169" t="n"/>
-      <c r="D10" s="103" t="n"/>
-      <c r="E10" s="104" t="n"/>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="106" t="n"/>
-      <c r="H10" s="117" t="n"/>
-      <c r="I10" s="105" t="n"/>
-      <c r="J10" s="105" t="n"/>
-      <c r="K10" s="105" t="n"/>
-      <c r="L10" s="108" t="n"/>
-      <c r="M10" s="167" t="n"/>
-      <c r="N10" s="115" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="118" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B11" s="101" t="n"/>
-      <c r="C11" s="169" t="n"/>
-      <c r="D11" s="103" t="n"/>
-      <c r="E11" s="104" t="n"/>
-      <c r="F11" s="105" t="n"/>
-      <c r="G11" s="106" t="n"/>
-      <c r="H11" s="107" t="n"/>
-      <c r="I11" s="105" t="n"/>
-      <c r="J11" s="105" t="n"/>
-      <c r="K11" s="105" t="n"/>
-      <c r="L11" s="108" t="n"/>
-      <c r="M11" s="167" t="n"/>
-      <c r="N11" s="115" t="n"/>
-      <c r="O11" s="105" t="n"/>
-      <c r="P11" s="118" t="n"/>
-    </row>
-    <row r="12" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B12" s="101" t="n"/>
-      <c r="C12" s="169" t="n"/>
-      <c r="D12" s="103" t="n"/>
-      <c r="E12" s="104" t="n"/>
-      <c r="F12" s="105" t="n"/>
-      <c r="G12" s="106" t="n"/>
-      <c r="H12" s="107" t="n"/>
-      <c r="I12" s="105" t="n"/>
-      <c r="J12" s="105" t="n"/>
-      <c r="K12" s="105" t="n"/>
-      <c r="L12" s="108" t="n"/>
-      <c r="M12" s="167" t="n"/>
-      <c r="N12" s="115" t="n"/>
-      <c r="O12" s="105" t="n"/>
-      <c r="P12" s="118" t="n"/>
-    </row>
-    <row r="13" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B13" s="101" t="n"/>
-      <c r="C13" s="170" t="n"/>
-      <c r="D13" s="121" t="n"/>
-      <c r="E13" s="122" t="n"/>
-      <c r="F13" s="123" t="n"/>
-      <c r="G13" s="124" t="n"/>
-      <c r="H13" s="125" t="n"/>
-      <c r="I13" s="123" t="n"/>
-      <c r="J13" s="123" t="n"/>
-      <c r="K13" s="123" t="n"/>
-      <c r="L13" s="126" t="n"/>
-      <c r="M13" s="171" t="n"/>
-      <c r="N13" s="128" t="n"/>
-      <c r="O13" s="123" t="n"/>
-      <c r="P13" s="129" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B14" s="101" t="n"/>
-      <c r="C14" s="170" t="n"/>
-      <c r="D14" s="121" t="n"/>
-      <c r="E14" s="122" t="n"/>
-      <c r="F14" s="123" t="n"/>
-      <c r="G14" s="124" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="123" t="n"/>
-      <c r="J14" s="123" t="n"/>
-      <c r="K14" s="123" t="n"/>
-      <c r="L14" s="126" t="n"/>
-      <c r="M14" s="171" t="n"/>
-      <c r="N14" s="123" t="n"/>
-      <c r="O14" s="123" t="n"/>
-      <c r="P14" s="129" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B15" s="101" t="n"/>
-      <c r="C15" s="166" t="n"/>
-      <c r="D15" s="103" t="n"/>
-      <c r="E15" s="104" t="n"/>
-      <c r="F15" s="105" t="n"/>
-      <c r="G15" s="106" t="n"/>
-      <c r="H15" s="107" t="n"/>
-      <c r="I15" s="105" t="n"/>
-      <c r="J15" s="105" t="n"/>
-      <c r="K15" s="105" t="n"/>
-      <c r="L15" s="108" t="n"/>
-      <c r="M15" s="167" t="n"/>
-      <c r="N15" s="130" t="n"/>
-      <c r="O15" s="130" t="n"/>
-      <c r="P15" s="131" t="n"/>
-    </row>
-    <row r="16" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B16" s="101" t="n"/>
-      <c r="C16" s="166" t="n"/>
-      <c r="D16" s="103" t="n"/>
-      <c r="E16" s="104" t="n"/>
-      <c r="F16" s="105" t="n"/>
-      <c r="G16" s="106" t="n"/>
-      <c r="H16" s="107" t="n"/>
-      <c r="I16" s="105" t="n"/>
-      <c r="J16" s="105" t="n"/>
-      <c r="K16" s="105" t="n"/>
-      <c r="L16" s="108" t="n"/>
-      <c r="M16" s="167" t="n"/>
-      <c r="N16" s="130" t="n"/>
-      <c r="O16" s="130" t="n"/>
-      <c r="P16" s="131" t="n"/>
-    </row>
-    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B17" s="101" t="n"/>
-      <c r="C17" s="166" t="n"/>
-      <c r="D17" s="103" t="n"/>
-      <c r="E17" s="104" t="n"/>
-      <c r="F17" s="105" t="n"/>
-      <c r="G17" s="106" t="n"/>
-      <c r="H17" s="107" t="n"/>
-      <c r="I17" s="105" t="n"/>
-      <c r="J17" s="105" t="n"/>
-      <c r="K17" s="105" t="n"/>
-      <c r="L17" s="108" t="n"/>
-      <c r="M17" s="167" t="n"/>
-      <c r="N17" s="130" t="n"/>
-      <c r="O17" s="130" t="n"/>
-      <c r="P17" s="131" t="n"/>
-    </row>
-    <row r="18" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B18" s="101" t="n"/>
-      <c r="C18" s="166" t="n"/>
-      <c r="D18" s="103" t="n"/>
-      <c r="E18" s="104" t="n"/>
-      <c r="F18" s="105" t="n"/>
-      <c r="G18" s="106" t="n"/>
-      <c r="H18" s="107" t="n"/>
-      <c r="I18" s="105" t="n"/>
-      <c r="J18" s="105" t="n"/>
-      <c r="K18" s="105" t="n"/>
-      <c r="L18" s="108" t="n"/>
-      <c r="M18" s="167" t="n"/>
-      <c r="N18" s="130" t="n"/>
-      <c r="O18" s="130" t="n"/>
-      <c r="P18" s="131" t="n"/>
-    </row>
-    <row r="19" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B19" s="101" t="n"/>
-      <c r="C19" s="166" t="n"/>
-      <c r="D19" s="103" t="n"/>
-      <c r="E19" s="104" t="n"/>
-      <c r="F19" s="105" t="n"/>
-      <c r="G19" s="106" t="n"/>
-      <c r="H19" s="107" t="n"/>
-      <c r="I19" s="105" t="n"/>
-      <c r="J19" s="105" t="n"/>
-      <c r="K19" s="105" t="n"/>
-      <c r="L19" s="108" t="n"/>
-      <c r="M19" s="167" t="n"/>
-      <c r="N19" s="130" t="n"/>
-      <c r="O19" s="130" t="n"/>
-      <c r="P19" s="131" t="n"/>
-    </row>
-    <row r="20" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B20" s="101" t="n"/>
-      <c r="C20" s="166" t="n"/>
-      <c r="D20" s="103" t="n"/>
-      <c r="E20" s="104" t="n"/>
-      <c r="F20" s="105" t="n"/>
-      <c r="G20" s="106" t="n"/>
-      <c r="H20" s="107" t="n"/>
-      <c r="I20" s="105" t="n"/>
-      <c r="J20" s="105" t="n"/>
-      <c r="K20" s="105" t="n"/>
-      <c r="L20" s="108" t="n"/>
-      <c r="M20" s="167" t="n"/>
-      <c r="N20" s="130" t="n"/>
-      <c r="O20" s="130" t="n"/>
-      <c r="P20" s="131" t="n"/>
-    </row>
-    <row r="21" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B21" s="101" t="n"/>
-      <c r="C21" s="166" t="n"/>
-      <c r="D21" s="103" t="n"/>
-      <c r="E21" s="104" t="n"/>
-      <c r="F21" s="105" t="n"/>
-      <c r="G21" s="106" t="n"/>
-      <c r="H21" s="107" t="n"/>
-      <c r="I21" s="105" t="n"/>
-      <c r="J21" s="105" t="n"/>
-      <c r="K21" s="105" t="n"/>
-      <c r="L21" s="108" t="n"/>
-      <c r="M21" s="167" t="n"/>
-      <c r="N21" s="130" t="n"/>
-      <c r="O21" s="130" t="n"/>
-      <c r="P21" s="131" t="n"/>
-    </row>
-    <row r="22" ht="12.75" customFormat="1" customHeight="1" s="80">
-      <c r="B22" s="101" t="n"/>
-      <c r="C22" s="166" t="n"/>
-      <c r="D22" s="103" t="n"/>
-      <c r="E22" s="104" t="n"/>
-      <c r="F22" s="105" t="n"/>
-      <c r="G22" s="106" t="n"/>
-      <c r="H22" s="107" t="n"/>
-      <c r="I22" s="105" t="n"/>
-      <c r="J22" s="105" t="n"/>
-      <c r="K22" s="105" t="n"/>
-      <c r="L22" s="108" t="n"/>
-      <c r="M22" s="167" t="n"/>
-      <c r="N22" s="130" t="n"/>
-      <c r="O22" s="130" t="n"/>
-      <c r="P22" s="131" t="n"/>
-    </row>
-    <row r="23" ht="13.5" customFormat="1" customHeight="1" s="82">
-      <c r="B23" s="132" t="n"/>
-      <c r="C23" s="133" t="n"/>
-      <c r="D23" s="133" t="n"/>
-      <c r="E23" s="133" t="n"/>
-      <c r="F23" s="133" t="n"/>
-      <c r="G23" s="133" t="n"/>
-      <c r="H23" s="134" t="n"/>
-      <c r="I23" s="134" t="n"/>
-      <c r="J23" s="134" t="n"/>
-      <c r="K23" s="134" t="n"/>
-      <c r="L23" s="134" t="n"/>
-      <c r="M23" s="172" t="n"/>
-      <c r="N23" s="134" t="n"/>
-      <c r="O23" s="134" t="n"/>
-      <c r="P23" s="136" t="n"/>
-    </row>
-    <row r="24" customFormat="1" s="83"/>
-    <row r="25" customFormat="1" s="83"/>
-    <row r="26" customFormat="1" s="83"/>
-    <row r="27" customFormat="1" s="83"/>
-    <row r="28" customFormat="1" s="83"/>
-    <row r="29" customFormat="1" s="83"/>
-    <row r="30" customFormat="1" s="83"/>
+      <c r="P4" s="106" t="n"/>
+    </row>
+    <row r="5" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B5" s="97" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C5" s="170" t="inlineStr">
+        <is>
+          <t>补充梁霁鸣负责模块（老人首页/健康档案/指标录入/家属端）RTM 详细说明，共 17 条（No.7~18、31~35），将占位文本替换为正式功能说明</t>
+        </is>
+      </c>
+      <c r="D5" s="99" t="inlineStr">
+        <is>
+          <t>设计用RTM</t>
+        </is>
+      </c>
+      <c r="E5" s="100" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="F5" s="101" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="G5" s="102" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" s="103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="101" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" s="101" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" s="104" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="M5" s="171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="N5" s="102" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="O5" s="102" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="P5" s="106" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B6" s="97" t="n"/>
+      <c r="C6" s="170" t="n"/>
+      <c r="D6" s="99" t="n"/>
+      <c r="E6" s="100" t="n"/>
+      <c r="F6" s="101" t="n"/>
+      <c r="G6" s="102" t="n"/>
+      <c r="H6" s="103" t="n"/>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="101" t="n"/>
+      <c r="K6" s="101" t="n"/>
+      <c r="L6" s="104" t="n"/>
+      <c r="M6" s="171" t="n"/>
+      <c r="N6" s="102" t="n"/>
+      <c r="O6" s="102" t="n"/>
+      <c r="P6" s="106" t="n"/>
+    </row>
+    <row r="7" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B7" s="97" t="n"/>
+      <c r="C7" s="170" t="n"/>
+      <c r="D7" s="99" t="n"/>
+      <c r="E7" s="100" t="n"/>
+      <c r="F7" s="101" t="n"/>
+      <c r="G7" s="102" t="n"/>
+      <c r="H7" s="103" t="n"/>
+      <c r="I7" s="101" t="n"/>
+      <c r="J7" s="101" t="n"/>
+      <c r="K7" s="101" t="n"/>
+      <c r="L7" s="104" t="n"/>
+      <c r="M7" s="171" t="n"/>
+      <c r="N7" s="101" t="n"/>
+      <c r="O7" s="102" t="n"/>
+      <c r="P7" s="106" t="n"/>
+    </row>
+    <row r="8" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B8" s="97" t="n"/>
+      <c r="C8" s="170" t="n"/>
+      <c r="D8" s="99" t="n"/>
+      <c r="E8" s="100" t="n"/>
+      <c r="F8" s="101" t="n"/>
+      <c r="G8" s="102" t="n"/>
+      <c r="H8" s="103" t="n"/>
+      <c r="I8" s="101" t="n"/>
+      <c r="J8" s="101" t="n"/>
+      <c r="K8" s="101" t="n"/>
+      <c r="L8" s="104" t="n"/>
+      <c r="M8" s="171" t="n"/>
+      <c r="N8" s="101" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="106" t="n"/>
+    </row>
+    <row r="9" ht="12" customFormat="1" customHeight="1" s="77">
+      <c r="B9" s="107" t="n"/>
+      <c r="C9" s="172" t="n"/>
+      <c r="D9" s="109" t="n"/>
+      <c r="E9" s="110" t="n"/>
+      <c r="F9" s="111" t="n"/>
+      <c r="G9" s="112" t="n"/>
+      <c r="H9" s="113" t="n"/>
+      <c r="I9" s="111" t="n"/>
+      <c r="J9" s="111" t="n"/>
+      <c r="K9" s="111" t="n"/>
+      <c r="L9" s="104" t="n"/>
+      <c r="M9" s="171" t="n"/>
+      <c r="N9" s="111" t="n"/>
+      <c r="O9" s="111" t="n"/>
+      <c r="P9" s="114" t="n"/>
+    </row>
+    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B10" s="97" t="n"/>
+      <c r="C10" s="173" t="n"/>
+      <c r="D10" s="99" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="101" t="n"/>
+      <c r="G10" s="102" t="n"/>
+      <c r="H10" s="113" t="n"/>
+      <c r="I10" s="101" t="n"/>
+      <c r="J10" s="101" t="n"/>
+      <c r="K10" s="101" t="n"/>
+      <c r="L10" s="104" t="n"/>
+      <c r="M10" s="171" t="n"/>
+      <c r="N10" s="111" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="114" t="n"/>
+    </row>
+    <row r="11" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B11" s="97" t="n"/>
+      <c r="C11" s="173" t="n"/>
+      <c r="D11" s="99" t="n"/>
+      <c r="E11" s="100" t="n"/>
+      <c r="F11" s="101" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="103" t="n"/>
+      <c r="I11" s="101" t="n"/>
+      <c r="J11" s="101" t="n"/>
+      <c r="K11" s="101" t="n"/>
+      <c r="L11" s="104" t="n"/>
+      <c r="M11" s="171" t="n"/>
+      <c r="N11" s="111" t="n"/>
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="114" t="n"/>
+    </row>
+    <row r="12" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B12" s="97" t="n"/>
+      <c r="C12" s="173" t="n"/>
+      <c r="D12" s="99" t="n"/>
+      <c r="E12" s="100" t="n"/>
+      <c r="F12" s="101" t="n"/>
+      <c r="G12" s="102" t="n"/>
+      <c r="H12" s="103" t="n"/>
+      <c r="I12" s="101" t="n"/>
+      <c r="J12" s="101" t="n"/>
+      <c r="K12" s="101" t="n"/>
+      <c r="L12" s="104" t="n"/>
+      <c r="M12" s="171" t="n"/>
+      <c r="N12" s="111" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="114" t="n"/>
+    </row>
+    <row r="13" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B13" s="97" t="n"/>
+      <c r="C13" s="174" t="n"/>
+      <c r="D13" s="117" t="n"/>
+      <c r="E13" s="118" t="n"/>
+      <c r="F13" s="119" t="n"/>
+      <c r="G13" s="120" t="n"/>
+      <c r="H13" s="121" t="n"/>
+      <c r="I13" s="119" t="n"/>
+      <c r="J13" s="119" t="n"/>
+      <c r="K13" s="119" t="n"/>
+      <c r="L13" s="122" t="n"/>
+      <c r="M13" s="175" t="n"/>
+      <c r="N13" s="124" t="n"/>
+      <c r="O13" s="119" t="n"/>
+      <c r="P13" s="125" t="n"/>
+    </row>
+    <row r="14" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B14" s="97" t="n"/>
+      <c r="C14" s="174" t="n"/>
+      <c r="D14" s="117" t="n"/>
+      <c r="E14" s="118" t="n"/>
+      <c r="F14" s="119" t="n"/>
+      <c r="G14" s="120" t="n"/>
+      <c r="H14" s="121" t="n"/>
+      <c r="I14" s="119" t="n"/>
+      <c r="J14" s="119" t="n"/>
+      <c r="K14" s="119" t="n"/>
+      <c r="L14" s="122" t="n"/>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="119" t="n"/>
+      <c r="O14" s="119" t="n"/>
+      <c r="P14" s="125" t="n"/>
+    </row>
+    <row r="15" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B15" s="97" t="n"/>
+      <c r="C15" s="170" t="n"/>
+      <c r="D15" s="99" t="n"/>
+      <c r="E15" s="100" t="n"/>
+      <c r="F15" s="101" t="n"/>
+      <c r="G15" s="102" t="n"/>
+      <c r="H15" s="103" t="n"/>
+      <c r="I15" s="101" t="n"/>
+      <c r="J15" s="101" t="n"/>
+      <c r="K15" s="101" t="n"/>
+      <c r="L15" s="104" t="n"/>
+      <c r="M15" s="171" t="n"/>
+      <c r="N15" s="126" t="n"/>
+      <c r="O15" s="126" t="n"/>
+      <c r="P15" s="127" t="n"/>
+    </row>
+    <row r="16" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B16" s="97" t="n"/>
+      <c r="C16" s="170" t="n"/>
+      <c r="D16" s="99" t="n"/>
+      <c r="E16" s="100" t="n"/>
+      <c r="F16" s="101" t="n"/>
+      <c r="G16" s="102" t="n"/>
+      <c r="H16" s="103" t="n"/>
+      <c r="I16" s="101" t="n"/>
+      <c r="J16" s="101" t="n"/>
+      <c r="K16" s="101" t="n"/>
+      <c r="L16" s="104" t="n"/>
+      <c r="M16" s="171" t="n"/>
+      <c r="N16" s="126" t="n"/>
+      <c r="O16" s="126" t="n"/>
+      <c r="P16" s="127" t="n"/>
+    </row>
+    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B17" s="97" t="n"/>
+      <c r="C17" s="170" t="n"/>
+      <c r="D17" s="99" t="n"/>
+      <c r="E17" s="100" t="n"/>
+      <c r="F17" s="101" t="n"/>
+      <c r="G17" s="102" t="n"/>
+      <c r="H17" s="103" t="n"/>
+      <c r="I17" s="101" t="n"/>
+      <c r="J17" s="101" t="n"/>
+      <c r="K17" s="101" t="n"/>
+      <c r="L17" s="104" t="n"/>
+      <c r="M17" s="171" t="n"/>
+      <c r="N17" s="126" t="n"/>
+      <c r="O17" s="126" t="n"/>
+      <c r="P17" s="127" t="n"/>
+    </row>
+    <row r="18" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B18" s="97" t="n"/>
+      <c r="C18" s="170" t="n"/>
+      <c r="D18" s="99" t="n"/>
+      <c r="E18" s="100" t="n"/>
+      <c r="F18" s="101" t="n"/>
+      <c r="G18" s="102" t="n"/>
+      <c r="H18" s="103" t="n"/>
+      <c r="I18" s="101" t="n"/>
+      <c r="J18" s="101" t="n"/>
+      <c r="K18" s="101" t="n"/>
+      <c r="L18" s="104" t="n"/>
+      <c r="M18" s="171" t="n"/>
+      <c r="N18" s="126" t="n"/>
+      <c r="O18" s="126" t="n"/>
+      <c r="P18" s="127" t="n"/>
+    </row>
+    <row r="19" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B19" s="97" t="n"/>
+      <c r="C19" s="170" t="n"/>
+      <c r="D19" s="99" t="n"/>
+      <c r="E19" s="100" t="n"/>
+      <c r="F19" s="101" t="n"/>
+      <c r="G19" s="102" t="n"/>
+      <c r="H19" s="103" t="n"/>
+      <c r="I19" s="101" t="n"/>
+      <c r="J19" s="101" t="n"/>
+      <c r="K19" s="101" t="n"/>
+      <c r="L19" s="104" t="n"/>
+      <c r="M19" s="171" t="n"/>
+      <c r="N19" s="126" t="n"/>
+      <c r="O19" s="126" t="n"/>
+      <c r="P19" s="127" t="n"/>
+    </row>
+    <row r="20" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B20" s="97" t="n"/>
+      <c r="C20" s="170" t="n"/>
+      <c r="D20" s="99" t="n"/>
+      <c r="E20" s="100" t="n"/>
+      <c r="F20" s="101" t="n"/>
+      <c r="G20" s="102" t="n"/>
+      <c r="H20" s="103" t="n"/>
+      <c r="I20" s="101" t="n"/>
+      <c r="J20" s="101" t="n"/>
+      <c r="K20" s="101" t="n"/>
+      <c r="L20" s="104" t="n"/>
+      <c r="M20" s="171" t="n"/>
+      <c r="N20" s="126" t="n"/>
+      <c r="O20" s="126" t="n"/>
+      <c r="P20" s="127" t="n"/>
+    </row>
+    <row r="21" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B21" s="97" t="n"/>
+      <c r="C21" s="170" t="n"/>
+      <c r="D21" s="99" t="n"/>
+      <c r="E21" s="100" t="n"/>
+      <c r="F21" s="101" t="n"/>
+      <c r="G21" s="102" t="n"/>
+      <c r="H21" s="103" t="n"/>
+      <c r="I21" s="101" t="n"/>
+      <c r="J21" s="101" t="n"/>
+      <c r="K21" s="101" t="n"/>
+      <c r="L21" s="104" t="n"/>
+      <c r="M21" s="171" t="n"/>
+      <c r="N21" s="126" t="n"/>
+      <c r="O21" s="126" t="n"/>
+      <c r="P21" s="127" t="n"/>
+    </row>
+    <row r="22" ht="12.75" customFormat="1" customHeight="1" s="76">
+      <c r="B22" s="97" t="n"/>
+      <c r="C22" s="170" t="n"/>
+      <c r="D22" s="99" t="n"/>
+      <c r="E22" s="100" t="n"/>
+      <c r="F22" s="101" t="n"/>
+      <c r="G22" s="102" t="n"/>
+      <c r="H22" s="103" t="n"/>
+      <c r="I22" s="101" t="n"/>
+      <c r="J22" s="101" t="n"/>
+      <c r="K22" s="101" t="n"/>
+      <c r="L22" s="104" t="n"/>
+      <c r="M22" s="171" t="n"/>
+      <c r="N22" s="126" t="n"/>
+      <c r="O22" s="126" t="n"/>
+      <c r="P22" s="127" t="n"/>
+    </row>
+    <row r="23" ht="13.5" customFormat="1" customHeight="1" s="78">
+      <c r="B23" s="128" t="n"/>
+      <c r="C23" s="129" t="n"/>
+      <c r="D23" s="129" t="n"/>
+      <c r="E23" s="129" t="n"/>
+      <c r="F23" s="129" t="n"/>
+      <c r="G23" s="129" t="n"/>
+      <c r="H23" s="130" t="n"/>
+      <c r="I23" s="130" t="n"/>
+      <c r="J23" s="130" t="n"/>
+      <c r="K23" s="130" t="n"/>
+      <c r="L23" s="130" t="n"/>
+      <c r="M23" s="176" t="n"/>
+      <c r="N23" s="130" t="n"/>
+      <c r="O23" s="130" t="n"/>
+      <c r="P23" s="132" t="n"/>
+    </row>
+    <row r="24" customFormat="1" s="79"/>
+    <row r="25" customFormat="1" s="79"/>
+    <row r="26" customFormat="1" s="79"/>
+    <row r="27" customFormat="1" s="79"/>
+    <row r="28" customFormat="1" s="79"/>
+    <row r="29" customFormat="1" s="79"/>
+    <row r="30" customFormat="1" s="79"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" scale="99" fitToHeight="0"/>
@@ -4301,20 +3756,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col width="0.875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.5" customWidth="1" style="9" min="2" max="2"/>
-    <col width="15.125" customWidth="1" style="9" min="3" max="3"/>
-    <col width="23" customWidth="1" style="9" min="4" max="4"/>
-    <col width="24.125" customWidth="1" style="9" min="5" max="5"/>
-    <col width="32.375" customWidth="1" style="9" min="6" max="6"/>
-    <col width="3.5" customWidth="1" style="9" min="7" max="7"/>
-    <col width="4.5" customWidth="1" style="9" min="8" max="8"/>
-    <col width="3.5" customWidth="1" style="9" min="9" max="9"/>
-    <col width="23" customWidth="1" style="10" min="10" max="10"/>
-    <col width="6.75" customWidth="1" style="10" min="11" max="11"/>
-    <col width="9" customWidth="1" style="11" min="12" max="16384"/>
+    <col width="0.90625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.453125" customWidth="1" style="166" min="2" max="2"/>
+    <col width="15.08984375" customWidth="1" style="166" min="3" max="3"/>
+    <col width="23" customWidth="1" style="166" min="4" max="4"/>
+    <col width="24.08984375" customWidth="1" style="166" min="5" max="5"/>
+    <col width="32.36328125" customWidth="1" style="166" min="6" max="6"/>
+    <col width="3.453125" customWidth="1" style="166" min="7" max="7"/>
+    <col width="4.453125" customWidth="1" style="166" min="8" max="8"/>
+    <col width="3.453125" customWidth="1" style="166" min="9" max="9"/>
+    <col width="23" customWidth="1" style="167" min="10" max="10"/>
+    <col width="6.7265625" customWidth="1" style="167" min="11" max="11"/>
+    <col width="9" customWidth="1" style="11" min="12" max="12"/>
+    <col width="9" customWidth="1" style="11" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customFormat="1" customHeight="1" s="1">
@@ -4333,7 +3789,7 @@
       <c r="J1" s="13" t="n"/>
       <c r="K1" s="13" t="n"/>
     </row>
-    <row r="2" customFormat="1" s="2">
+    <row r="2" ht="14" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="15" t="inlineStr">
         <is>
@@ -4387,20 +3843,20 @@
           <t>小分類</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="163" t="inlineStr">
         <is>
           <t>详细说明</t>
         </is>
       </c>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="24" t="n"/>
+      <c r="J4" s="163" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="161" t="inlineStr">
         <is>
           <t>责任者</t>
         </is>
@@ -4408,75 +3864,75 @@
     </row>
     <row r="5" ht="13.5" customFormat="1" customHeight="1" s="3">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>（模块）</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>（子模块）</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>（功能点）</t>
         </is>
       </c>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="30" t="inlineStr">
+      <c r="F5" s="164" t="n"/>
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>UT</t>
         </is>
       </c>
-      <c r="J5" s="29" t="n"/>
-      <c r="K5" s="31" t="n"/>
+      <c r="J5" s="164" t="n"/>
+      <c r="K5" s="162" t="n"/>
     </row>
     <row r="6" ht="34" customFormat="1" customHeight="1" s="4">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>认证（登录/注册）</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>登录界面</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>header</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>登录页顶部展示系统名称“康养健康助手”。</t>
         </is>
       </c>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="37" t="inlineStr">
+      <c r="G6" s="32" t="n"/>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="32" t="n"/>
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K6" s="38" t="inlineStr">
+      <c r="K6" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -4484,30 +3940,30 @@
     </row>
     <row r="7" ht="34" customFormat="1" customHeight="1" s="4">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>手机号输入框：占位提示“手机号”，仅允许输入数字。</t>
         </is>
       </c>
-      <c r="G7" s="43" t="n"/>
-      <c r="H7" s="43" t="n"/>
-      <c r="I7" s="43" t="n"/>
-      <c r="J7" s="37" t="inlineStr">
+      <c r="G7" s="39" t="n"/>
+      <c r="H7" s="39" t="n"/>
+      <c r="I7" s="39" t="n"/>
+      <c r="J7" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K7" s="38" t="inlineStr">
+      <c r="K7" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -4515,30 +3971,30 @@
     </row>
     <row r="8" ht="34" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>密码输入框：输入内容以圆点遮蔽，防止窥视。</t>
         </is>
       </c>
-      <c r="G8" s="43" t="n"/>
-      <c r="H8" s="43" t="n"/>
-      <c r="I8" s="43" t="n"/>
-      <c r="J8" s="37" t="inlineStr">
+      <c r="G8" s="39" t="n"/>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="39" t="n"/>
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K8" s="38" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -4546,30 +4002,30 @@
     </row>
     <row r="9" ht="76" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>点击“登录”校验手机号与密码非空；成功后按角色（老人/家属/护工/管理员）签发JWT并跳转对应首页；失败提示“手机号或密码错误！”。</t>
         </is>
       </c>
-      <c r="G9" s="43" t="n"/>
-      <c r="H9" s="43" t="n"/>
-      <c r="I9" s="43" t="n"/>
-      <c r="J9" s="37" t="inlineStr">
+      <c r="G9" s="39" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="39" t="n"/>
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K9" s="38" t="inlineStr">
+      <c r="K9" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -4577,30 +4033,30 @@
     </row>
     <row r="10" ht="34" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="47" t="inlineStr">
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="43" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="F10" s="46" t="inlineStr">
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>提供“没有账号？点击注册”入口，点击切换至注册页。</t>
         </is>
       </c>
-      <c r="G10" s="43" t="n"/>
-      <c r="H10" s="43" t="n"/>
-      <c r="I10" s="43" t="n"/>
-      <c r="J10" s="37" t="inlineStr">
+      <c r="G10" s="39" t="n"/>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="39" t="n"/>
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K10" s="38" t="inlineStr">
+      <c r="K10" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -4608,442 +4064,442 @@
     </row>
     <row r="11" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>注册界面</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>header+actions</t>
         </is>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>注册页：校验手机号格式与密码强度，需勾选健康数据隐私授权，成功后创建账号并跳转登录页。</t>
         </is>
       </c>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
-      <c r="J11" s="37" t="inlineStr">
+      <c r="G11" s="39" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="39" t="n"/>
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K11" s="38" t="inlineStr">
+      <c r="K11" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33.75" customFormat="1" customHeight="1" s="4">
+    <row r="12" ht="78.5" customFormat="1" customHeight="1" s="4">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="39" t="n">
+      <c r="B12" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>老人首页（适老化）</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>header</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>页面标题+健康卡片</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>老人首页顶部展示系统名称“康养健康助手”；主体为健康卡片区，以大字号（≥18px）、高对比配色展示今日关键指标卡片（血压/心率/血糖），主要按钮点按区域充足（≥48px），指标异常时以警示色高亮并提示“有预警”。</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="39" t="n"/>
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G12" s="43" t="n"/>
-      <c r="H12" s="43" t="n"/>
-      <c r="I12" s="43" t="n"/>
-      <c r="J12" s="37" t="inlineStr">
+      <c r="K12" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customFormat="1" customHeight="1" s="4">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>nav</t>
+        </is>
+      </c>
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>档案入口</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>首页导航提供“我的档案”入口，一键直达健康档案列表；入口为大按钮、高对比，从首页到查看档案主流程 ≤3 步。</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="39" t="n"/>
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K12" s="38" t="inlineStr">
+      <c r="K13" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="38.25" customFormat="1" customHeight="1" s="4">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="41" t="inlineStr">
-        <is>
-          <t>nav</t>
-        </is>
-      </c>
-      <c r="E13" s="42" t="inlineStr">
-        <is>
-          <t>档案入口</t>
-        </is>
-      </c>
-      <c r="F13" s="41" t="inlineStr">
+    <row r="14" ht="42.5" customFormat="1" customHeight="1" s="4">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>AI咨询入口</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>首页导航提供“AI 健康咨询”入口，一键直达咨询页；入口位于首页显要位置，便于老人以最短路径发起咨询。</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="n"/>
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="39" t="n"/>
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="43" t="n"/>
-      <c r="I13" s="43" t="n"/>
-      <c r="J13" s="37" t="inlineStr">
+      <c r="K14" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55.5" customFormat="1" customHeight="1" s="4">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>预警入口</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>首页导航提供“我的预警”入口；存在未处理预警时入口带红色角标并显示数量，点击直达通知中心查看待处理预警。</t>
+        </is>
+      </c>
+      <c r="G15" s="39" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="39" t="n"/>
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K13" s="38" t="inlineStr">
+      <c r="K15" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="39.75" customFormat="1" customHeight="1" s="4">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="42" t="inlineStr">
-        <is>
-          <t>AI咨询入口</t>
-        </is>
-      </c>
-      <c r="F14" s="41" t="inlineStr">
+    <row r="16" ht="61" customFormat="1" customHeight="1" s="4">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>toolbar</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>一键朗读</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>首页工具栏提供“一键朗读”按钮，点击调用浏览器 Web Speech API 语音朗读页面主要文本，再次点击停止，降低老人阅读门槛。</t>
+        </is>
+      </c>
+      <c r="G16" s="39" t="n"/>
+      <c r="H16" s="39" t="n"/>
+      <c r="I16" s="39" t="n"/>
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G14" s="43" t="n"/>
-      <c r="H14" s="43" t="n"/>
-      <c r="I14" s="43" t="n"/>
-      <c r="J14" s="37" t="inlineStr">
+      <c r="K16" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="74" customFormat="1" customHeight="1" s="4">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>关怀提醒</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>首页工具栏展示关怀提醒条，登录后显示当日用药提醒与健康打卡提醒，点击可跳转至对应功能入口。</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="n"/>
+      <c r="H17" s="48" t="n"/>
+      <c r="I17" s="48" t="n"/>
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K14" s="38" t="inlineStr">
+      <c r="K17" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customFormat="1" customHeight="1" s="4">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="42" t="inlineStr">
-        <is>
-          <t>预警入口</t>
-        </is>
-      </c>
-      <c r="F15" s="41" t="inlineStr">
+    <row r="18" ht="74" customFormat="1" customHeight="1" s="4">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>健康档案</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>档案列表</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>档案切换与查看</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>档案列表页展示当前用户可见的全部档案（本人/代管老人），支持多档案间快速切换；点选档案展示基本信息、既往病史与慢病标签，列表按最近更新时间排序。</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="39" t="n"/>
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G15" s="43" t="n"/>
-      <c r="H15" s="43" t="n"/>
-      <c r="I15" s="43" t="n"/>
-      <c r="J15" s="37" t="inlineStr">
+      <c r="K18" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="74" customFormat="1" customHeight="1" s="4">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>档案表单</t>
+        </is>
+      </c>
+      <c r="E19" s="52" t="inlineStr">
+        <is>
+          <t>创建档案</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>创建档案表单：填写姓名、性别、年龄、联系电话、既往病史与慢病标签（多选）；保存前校验必填项，成功后创建档案并跳转档案详情页。</t>
+        </is>
+      </c>
+      <c r="G19" s="53" t="n"/>
+      <c r="H19" s="53" t="n"/>
+      <c r="I19" s="53" t="n"/>
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K15" s="38" t="inlineStr">
+      <c r="K19" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="40.5" customFormat="1" customHeight="1" s="4">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="41" t="inlineStr">
-        <is>
-          <t>toolbar</t>
-        </is>
-      </c>
-      <c r="E16" s="42" t="inlineStr">
-        <is>
-          <t>一键朗读</t>
-        </is>
-      </c>
-      <c r="F16" s="41" t="inlineStr">
+    <row r="20" ht="74" customFormat="1" customHeight="1" s="4">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>编辑与删除档案</t>
+        </is>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>档案详情页提供“编辑”与“删除”操作；编辑可修改基本资料与慢病标签；删除需二次确认，确认后删除该档案及其关联数据，代管关系同步解除。</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G16" s="43" t="n"/>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
-      <c r="J16" s="37" t="inlineStr">
+      <c r="K20" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60.5" customFormat="1" customHeight="1" s="4">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>指标录入</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>录入表单</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>血压录入</t>
+        </is>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>血压录入表单：录入收缩压/舒张压（单位 mmHg），前端做范围校验并校验收缩压 &gt; 舒张压；支持选择测量时间，异常值即时提示。</t>
+        </is>
+      </c>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K16" s="38" t="inlineStr">
+      <c r="K21" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="41.25" customFormat="1" customHeight="1" s="4">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="50" t="n"/>
-      <c r="E17" s="51" t="inlineStr">
-        <is>
-          <t>关怀提醒</t>
-        </is>
-      </c>
-      <c r="F17" s="50" t="inlineStr">
+    <row r="22" ht="56.5" customFormat="1" customHeight="1" s="4">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>心率与血糖录入</t>
+        </is>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>心率与血糖录入：心率（单位 次/分）与血糖（单位 mmol/L，可标注空腹/餐后）分别录入，前端做范围校验，录入后写入统一指标表。</t>
+        </is>
+      </c>
+      <c r="G22" s="39" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="39" t="n"/>
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="37" t="inlineStr">
+      <c r="K22" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="74" customFormat="1" customHeight="1" s="4">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>保存录入+趋势图</t>
+        </is>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
+        <is>
+          <t>指标保存后写入统一健康记录表（type 字段区分指标类型）；页面展示近 30 天指标趋势曲线（ECharts），超阈值数据点以警示色高亮标注，支持切换指标类型查看。</t>
+        </is>
+      </c>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K17" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38.25" customFormat="1" customHeight="1" s="4">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>健康档案</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>档案列表</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>档案切换与查看</t>
-        </is>
-      </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="n"/>
-      <c r="I18" s="43" t="n"/>
-      <c r="J18" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K18" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="27" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="53" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="55" t="inlineStr">
-        <is>
-          <t>档案表单</t>
-        </is>
-      </c>
-      <c r="E19" s="56" t="inlineStr">
-        <is>
-          <t>创建档案</t>
-        </is>
-      </c>
-      <c r="F19" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G19" s="57" t="n"/>
-      <c r="H19" s="57" t="n"/>
-      <c r="I19" s="57" t="n"/>
-      <c r="J19" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K19" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36.75" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" s="40" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="42" t="inlineStr">
-        <is>
-          <t>编辑与删除档案</t>
-        </is>
-      </c>
-      <c r="F20" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="43" t="n"/>
-      <c r="J20" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K20" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="44" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>指标录入</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="inlineStr">
-        <is>
-          <t>录入表单</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="inlineStr">
-        <is>
-          <t>血压录入</t>
-        </is>
-      </c>
-      <c r="F21" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G21" s="43" t="n"/>
-      <c r="H21" s="43" t="n"/>
-      <c r="I21" s="43" t="n"/>
-      <c r="J21" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K21" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="41.25" customFormat="1" customHeight="1" s="4">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="39" t="n">
-        <v>17</v>
-      </c>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="42" t="inlineStr">
-        <is>
-          <t>心率与血糖录入</t>
-        </is>
-      </c>
-      <c r="F22" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G22" s="43" t="n"/>
-      <c r="H22" s="43" t="n"/>
-      <c r="I22" s="43" t="n"/>
-      <c r="J22" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K22" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.25" customFormat="1" customHeight="1" s="4">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="53" t="n">
-        <v>18</v>
-      </c>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="42" t="inlineStr">
-        <is>
-          <t>保存录入+趋势图</t>
-        </is>
-      </c>
-      <c r="F23" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G23" s="43" t="n"/>
-      <c r="H23" s="43" t="n"/>
-      <c r="I23" s="43" t="n"/>
-      <c r="J23" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K23" s="38" t="inlineStr">
+      <c r="K23" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5051,38 +4507,38 @@
     </row>
     <row r="24" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="39" t="n">
+      <c r="B24" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>AI咨询</t>
         </is>
       </c>
-      <c r="D24" s="41" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>header</t>
         </is>
       </c>
-      <c r="E24" s="42" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>页面标题+档案选择</t>
         </is>
       </c>
-      <c r="F24" s="55" t="inlineStr">
+      <c r="F24" s="51" t="inlineStr">
         <is>
           <t>AI健康咨询页：标题“AI健康咨询”，提供咨询档案下拉切换，选中档案后咨询基于该档案数据。</t>
         </is>
       </c>
-      <c r="G24" s="43" t="n"/>
-      <c r="H24" s="43" t="n"/>
-      <c r="I24" s="43" t="n"/>
-      <c r="J24" s="37" t="inlineStr">
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K24" s="38" t="inlineStr">
+      <c r="K24" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5090,34 +4546,34 @@
     </row>
     <row r="25" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="44" t="n">
+      <c r="B25" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="58" t="n"/>
-      <c r="D25" s="41" t="inlineStr">
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>chat</t>
         </is>
       </c>
-      <c r="E25" s="42" t="inlineStr">
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>问答消息列表</t>
         </is>
       </c>
-      <c r="F25" s="55" t="inlineStr">
+      <c r="F25" s="51" t="inlineStr">
         <is>
           <t>问答消息列表：用户消息与AI回复分列展示，新消息自动滚动到底部，AI长文分段分点呈现。</t>
         </is>
       </c>
-      <c r="G25" s="43" t="n"/>
-      <c r="H25" s="43" t="n"/>
-      <c r="I25" s="43" t="n"/>
-      <c r="J25" s="37" t="inlineStr">
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K25" s="38" t="inlineStr">
+      <c r="K25" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5125,96 +4581,96 @@
     </row>
     <row r="26" ht="34" customFormat="1" customHeight="1" s="4">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="48" t="n">
+      <c r="B26" s="44" t="n">
         <v>21</v>
       </c>
-      <c r="C26" s="59" t="n"/>
-      <c r="D26" s="46" t="n"/>
-      <c r="E26" s="47" t="inlineStr">
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="43" t="inlineStr">
         <is>
           <t>预设问题按钮</t>
         </is>
       </c>
-      <c r="F26" s="60" t="inlineStr">
+      <c r="F26" s="56" t="inlineStr">
         <is>
           <t>提供“血压高怎么办”“用药时间”等预设问题按钮，免打字即点即问。</t>
         </is>
       </c>
-      <c r="G26" s="43" t="n"/>
-      <c r="H26" s="43" t="n"/>
-      <c r="I26" s="43" t="n"/>
-      <c r="J26" s="37" t="inlineStr">
+      <c r="G26" s="39" t="n"/>
+      <c r="H26" s="39" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K26" s="38" t="inlineStr">
+      <c r="K26" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customFormat="1" customHeight="1" s="5">
-      <c r="A27" s="61" t="n"/>
-      <c r="B27" s="32" t="n">
+      <c r="A27" s="57" t="n"/>
+      <c r="B27" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="C27" s="58" t="n"/>
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="E27" s="35" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>提问输入框</t>
         </is>
       </c>
-      <c r="F27" s="34" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>提问输入框：输入健康问题，内容为空时拦截发送。</t>
         </is>
       </c>
-      <c r="G27" s="57" t="n"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="37" t="inlineStr">
+      <c r="G27" s="53" t="n"/>
+      <c r="H27" s="53" t="n"/>
+      <c r="I27" s="53" t="n"/>
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K27" s="38" t="inlineStr">
+      <c r="K27" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
     <row r="28" ht="62" customFormat="1" customHeight="1" s="6">
-      <c r="A28" s="63" t="n"/>
-      <c r="B28" s="53" t="n">
+      <c r="A28" s="59" t="n"/>
+      <c r="B28" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="C28" s="64" t="n"/>
-      <c r="D28" s="55" t="n"/>
-      <c r="E28" s="56" t="inlineStr">
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="51" t="n"/>
+      <c r="E28" s="52" t="inlineStr">
         <is>
           <t>发送与智能路由</t>
         </is>
       </c>
-      <c r="F28" s="55" t="inlineStr">
+      <c r="F28" s="51" t="inlineStr">
         <is>
           <t>发送后由后端组装（档案摘要+问题）调用LLM接口，按意图路由（普通/数据/异常/紧急）返回建议，支持流式输出。</t>
         </is>
       </c>
-      <c r="G28" s="57" t="n"/>
-      <c r="H28" s="57" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="37" t="inlineStr">
+      <c r="G28" s="53" t="n"/>
+      <c r="H28" s="53" t="n"/>
+      <c r="I28" s="53" t="n"/>
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>丘宇乾/梁霁鸣/周彦龙</t>
         </is>
       </c>
-      <c r="K28" s="38" t="inlineStr">
+      <c r="K28" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5222,34 +4678,34 @@
     </row>
     <row r="29" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="53" t="n">
+      <c r="B29" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="C29" s="54" t="n"/>
-      <c r="D29" s="55" t="inlineStr">
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="51" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
-      <c r="E29" s="56" t="inlineStr">
+      <c r="E29" s="52" t="inlineStr">
         <is>
           <t>历史记录与免责声明</t>
         </is>
       </c>
-      <c r="F29" s="55" t="inlineStr">
+      <c r="F29" s="51" t="inlineStr">
         <is>
           <t>支持按档案查看历史问答并可回看；页面固定展示免责声明“内容仅供参考，不构成医疗诊断”。</t>
         </is>
       </c>
-      <c r="G29" s="57" t="n"/>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="37" t="inlineStr">
+      <c r="G29" s="53" t="n"/>
+      <c r="H29" s="53" t="n"/>
+      <c r="I29" s="53" t="n"/>
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K29" s="38" t="inlineStr">
+      <c r="K29" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5257,38 +4713,38 @@
     </row>
     <row r="30" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="65" t="n">
+      <c r="B30" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="54" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>预警中心</t>
         </is>
       </c>
-      <c r="D30" s="55" t="inlineStr">
+      <c r="D30" s="51" t="inlineStr">
         <is>
           <t>预警规则</t>
         </is>
       </c>
-      <c r="E30" s="56" t="inlineStr">
+      <c r="E30" s="52" t="inlineStr">
         <is>
           <t>主动预警与阈值引擎</t>
         </is>
       </c>
-      <c r="F30" s="55" t="inlineStr">
+      <c r="F30" s="51" t="inlineStr">
         <is>
           <t>新健康数据写入后自动进行阈值检测，命中即触发预警；阈值存于sys_config配置项，不写死。</t>
         </is>
       </c>
-      <c r="G30" s="57" t="n"/>
-      <c r="H30" s="57" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="37" t="inlineStr">
+      <c r="G30" s="53" t="n"/>
+      <c r="H30" s="53" t="n"/>
+      <c r="I30" s="53" t="n"/>
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K30" s="38" t="inlineStr">
+      <c r="K30" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5296,30 +4752,30 @@
     </row>
     <row r="31" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="39" t="n">
+      <c r="B31" s="35" t="n">
         <v>26</v>
       </c>
-      <c r="C31" s="54" t="n"/>
-      <c r="D31" s="55" t="n"/>
-      <c r="E31" s="56" t="inlineStr">
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="51" t="n"/>
+      <c r="E31" s="52" t="inlineStr">
         <is>
           <t>风险分级与AI摘要</t>
         </is>
       </c>
-      <c r="F31" s="55" t="inlineStr">
+      <c r="F31" s="51" t="inlineStr">
         <is>
           <t>风险等级分 正常/轻度/较高/高风险（0~3级）；AI结合历史趋势生成个性化预警摘要。</t>
         </is>
       </c>
-      <c r="G31" s="43" t="n"/>
-      <c r="H31" s="43" t="n"/>
-      <c r="I31" s="43" t="n"/>
-      <c r="J31" s="37" t="inlineStr">
+      <c r="G31" s="39" t="n"/>
+      <c r="H31" s="39" t="n"/>
+      <c r="I31" s="39" t="n"/>
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K31" s="38" t="inlineStr">
+      <c r="K31" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5327,34 +4783,34 @@
     </row>
     <row r="32" ht="62" customFormat="1" customHeight="1" s="4">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="53" t="n">
+      <c r="B32" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="C32" s="40" t="n"/>
-      <c r="D32" s="41" t="inlineStr">
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="37" t="inlineStr">
         <is>
           <t>预警列表</t>
         </is>
       </c>
-      <c r="E32" s="42" t="inlineStr">
+      <c r="E32" s="38" t="inlineStr">
         <is>
           <t>预警列表与详情</t>
         </is>
       </c>
-      <c r="F32" s="60" t="inlineStr">
+      <c r="F32" s="56" t="inlineStr">
         <is>
           <t>预警列表展示指标值/触发时间/风险等级，可查看详情（指标值、阈值、近30天趋势）；处理状态：待处理/已查看/已处理。</t>
         </is>
       </c>
-      <c r="G32" s="43" t="n"/>
-      <c r="H32" s="43" t="n"/>
-      <c r="I32" s="43" t="n"/>
-      <c r="J32" s="37" t="inlineStr">
+      <c r="G32" s="39" t="n"/>
+      <c r="H32" s="39" t="n"/>
+      <c r="I32" s="39" t="n"/>
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K32" s="38" t="inlineStr">
+      <c r="K32" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5362,34 +4818,34 @@
     </row>
     <row r="33" ht="62" customFormat="1" customHeight="1" s="4">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="39" t="n">
+      <c r="B33" s="35" t="n">
         <v>28</v>
       </c>
-      <c r="C33" s="40" t="n"/>
-      <c r="D33" s="41" t="inlineStr">
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>预警通知</t>
         </is>
       </c>
-      <c r="E33" s="42" t="inlineStr">
+      <c r="E33" s="38" t="inlineStr">
         <is>
           <t>分级推送</t>
         </is>
       </c>
-      <c r="F33" s="41" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>预警自动推送：老人首页提醒+角标，已绑定家属端同步通知，高风险升级通知护工后台；通知中心汇总所有预警并区分已读/未读。</t>
         </is>
       </c>
-      <c r="G33" s="43" t="n"/>
-      <c r="H33" s="43" t="n"/>
-      <c r="I33" s="43" t="n"/>
-      <c r="J33" s="37" t="inlineStr">
+      <c r="G33" s="39" t="n"/>
+      <c r="H33" s="39" t="n"/>
+      <c r="I33" s="39" t="n"/>
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K33" s="38" t="inlineStr">
+      <c r="K33" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5397,34 +4853,34 @@
     </row>
     <row r="34" ht="62" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="39" t="n">
+      <c r="B34" s="35" t="n">
         <v>29</v>
       </c>
-      <c r="C34" s="40" t="n"/>
-      <c r="D34" s="41" t="inlineStr">
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="37" t="inlineStr">
         <is>
           <t>预警处理</t>
         </is>
       </c>
-      <c r="E34" s="42" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>处理闭环</t>
         </is>
       </c>
-      <c r="F34" s="55" t="inlineStr">
+      <c r="F34" s="51" t="inlineStr">
         <is>
           <t>预警处理闭环：状态流转 待处理→已查看→已处理；家属/护工登记处理结论并留操作日志，标记已处理需填写处理结果。</t>
         </is>
       </c>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="43" t="n"/>
-      <c r="I34" s="43" t="n"/>
-      <c r="J34" s="37" t="inlineStr">
+      <c r="G34" s="39" t="n"/>
+      <c r="H34" s="39" t="n"/>
+      <c r="I34" s="39" t="n"/>
+      <c r="J34" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K34" s="38" t="inlineStr">
+      <c r="K34" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5432,205 +4888,205 @@
     </row>
     <row r="35" ht="48" customFormat="1" customHeight="1" s="4">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>预警通知</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>频率控制</t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>同一异常预警设冷静期/频率控制，短时间内同源异常合并去重，避免重复轰炸式通知。</t>
         </is>
       </c>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
-      <c r="J35" s="37" t="inlineStr">
+      <c r="G35" s="39" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="39" t="n"/>
+      <c r="J35" s="33" t="inlineStr">
         <is>
           <t>丘宇乾</t>
         </is>
       </c>
-      <c r="K35" s="38" t="inlineStr">
+      <c r="K35" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="50.25" customFormat="1" customHeight="1" s="4">
+    <row r="36" ht="71" customFormat="1" customHeight="1" s="4">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="53" t="n">
+      <c r="B36" s="49" t="n">
         <v>31</v>
       </c>
-      <c r="C36" s="54" t="inlineStr">
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>家属端</t>
         </is>
       </c>
-      <c r="D36" s="55" t="inlineStr">
+      <c r="D36" s="51" t="inlineStr">
         <is>
           <t>代管</t>
         </is>
       </c>
-      <c r="E36" s="56" t="inlineStr">
+      <c r="E36" s="52" t="inlineStr">
         <is>
           <t>绑定与代管老人</t>
         </is>
       </c>
-      <c r="F36" s="55" t="inlineStr">
+      <c r="F36" s="51" t="inlineStr">
+        <is>
+          <t>家属通过手机号/邀请码绑定老人档案建立代管关系，支持绑定并代管多位老人；列表展示每位被代管老人姓名、头像与最新健康状态；可解除绑定，权限随之失效。</t>
+        </is>
+      </c>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="n"/>
+      <c r="I36" s="39" t="n"/>
+      <c r="J36" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G36" s="43" t="n"/>
-      <c r="H36" s="43" t="n"/>
-      <c r="I36" s="43" t="n"/>
-      <c r="J36" s="37" t="inlineStr">
+      <c r="K36" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="71" customFormat="1" customHeight="1" s="4">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>健康看板</t>
+        </is>
+      </c>
+      <c r="E37" s="52" t="inlineStr">
+        <is>
+          <t>代管老人概况</t>
+        </is>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>家属健康看板汇总展示所有代管老人的健康概况，每位老人一张卡片（姓名/今日关键指标/健康状态标签）；状态分 正常/关注/异常 分色标识，点击进入该老人详情。</t>
+        </is>
+      </c>
+      <c r="G37" s="39" t="n"/>
+      <c r="H37" s="39" t="n"/>
+      <c r="I37" s="39" t="n"/>
+      <c r="J37" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K36" s="38" t="inlineStr">
+      <c r="K37" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customFormat="1" customHeight="1" s="4">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="53" t="n">
-        <v>32</v>
-      </c>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="55" t="inlineStr">
-        <is>
-          <t>健康看板</t>
-        </is>
-      </c>
-      <c r="E37" s="56" t="inlineStr">
-        <is>
-          <t>代管老人概况</t>
-        </is>
-      </c>
-      <c r="F37" s="55" t="inlineStr">
+    <row r="38" ht="71" customFormat="1" customHeight="1" s="6">
+      <c r="A38" s="59" t="n"/>
+      <c r="B38" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="37" t="n"/>
+      <c r="E38" s="38" t="inlineStr">
+        <is>
+          <t>看趋势与代录数据</t>
+        </is>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>家属可查看代管老人近 30 天健康指标趋势图；并可代老人录入血压/心率/血糖等指标，录入流程与老人端一致，数据归属该老人档案。</t>
+        </is>
+      </c>
+      <c r="G38" s="39" t="n"/>
+      <c r="H38" s="39" t="n"/>
+      <c r="I38" s="39" t="n"/>
+      <c r="J38" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G37" s="43" t="n"/>
-      <c r="H37" s="43" t="n"/>
-      <c r="I37" s="43" t="n"/>
-      <c r="J37" s="37" t="inlineStr">
+      <c r="K38" s="34" t="inlineStr">
+        <is>
+          <t>组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="71" customFormat="1" customHeight="1" s="7">
+      <c r="A39" s="62" t="n"/>
+      <c r="B39" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="37" t="inlineStr">
+        <is>
+          <t>预警</t>
+        </is>
+      </c>
+      <c r="E39" s="38" t="inlineStr">
+        <is>
+          <t>接收预警与代管咨询</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr">
+        <is>
+          <t>家属端接收代管老人的分级预警通知（与老人端首页提醒同步）；家属可以代管老人身份发起 AI 健康咨询，咨询基于该老人档案数据。</t>
+        </is>
+      </c>
+      <c r="G39" s="39" t="n"/>
+      <c r="H39" s="39" t="n"/>
+      <c r="I39" s="39" t="n"/>
+      <c r="J39" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="K37" s="38" t="inlineStr">
+      <c r="K39" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customFormat="1" customHeight="1" s="6">
-      <c r="A38" s="63" t="n"/>
-      <c r="B38" s="39" t="n">
-        <v>33</v>
-      </c>
-      <c r="C38" s="40" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="42" t="inlineStr">
-        <is>
-          <t>看趋势与代录数据</t>
-        </is>
-      </c>
-      <c r="F38" s="55" t="inlineStr">
+    <row r="40" ht="71" customFormat="1" customHeight="1" s="4">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="51" t="n"/>
+      <c r="E40" s="52" t="inlineStr">
+        <is>
+          <t>确认处理与通知中心</t>
+        </is>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>家属对代管老人预警登记处理（如“已处理/已联系老人”），处理结果留痕；通知中心汇总所有代管老人预警，区分已读/未读，支持查看预警详情（指标值/阈值/近 30 天趋势）。</t>
+        </is>
+      </c>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
+      <c r="I40" s="53" t="n"/>
+      <c r="J40" s="33" t="inlineStr">
         <is>
           <t>梁霁鸣</t>
         </is>
       </c>
-      <c r="G38" s="43" t="n"/>
-      <c r="H38" s="43" t="n"/>
-      <c r="I38" s="43" t="n"/>
-      <c r="J38" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K38" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="39" customFormat="1" customHeight="1" s="7">
-      <c r="A39" s="66" t="n"/>
-      <c r="B39" s="39" t="n">
-        <v>34</v>
-      </c>
-      <c r="C39" s="40" t="n"/>
-      <c r="D39" s="41" t="inlineStr">
-        <is>
-          <t>预警</t>
-        </is>
-      </c>
-      <c r="E39" s="42" t="inlineStr">
-        <is>
-          <t>接收预警与代管咨询</t>
-        </is>
-      </c>
-      <c r="F39" s="41" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G39" s="43" t="n"/>
-      <c r="H39" s="43" t="n"/>
-      <c r="I39" s="43" t="n"/>
-      <c r="J39" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K39" s="38" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38.25" customFormat="1" customHeight="1" s="4">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="53" t="n">
-        <v>35</v>
-      </c>
-      <c r="C40" s="54" t="n"/>
-      <c r="D40" s="55" t="n"/>
-      <c r="E40" s="56" t="inlineStr">
-        <is>
-          <t>确认处理与通知中心</t>
-        </is>
-      </c>
-      <c r="F40" s="55" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="G40" s="57" t="n"/>
-      <c r="H40" s="57" t="n"/>
-      <c r="I40" s="57" t="n"/>
-      <c r="J40" s="37" t="inlineStr">
-        <is>
-          <t>梁霁鸣</t>
-        </is>
-      </c>
-      <c r="K40" s="38" t="inlineStr">
+      <c r="K40" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5638,38 +5094,38 @@
     </row>
     <row r="41" ht="76" customFormat="1" customHeight="1" s="4">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="53" t="n">
+      <c r="B41" s="49" t="n">
         <v>36</v>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>护工端</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D41" s="37" t="inlineStr">
         <is>
           <t>老人工作台</t>
         </is>
       </c>
-      <c r="E41" s="42" t="inlineStr">
+      <c r="E41" s="38" t="inlineStr">
         <is>
           <t>负责老人列表与状态标识</t>
         </is>
       </c>
-      <c r="F41" s="55" t="inlineStr">
+      <c r="F41" s="51" t="inlineStr">
         <is>
           <t>护工工作台：展示负责老人卡片（姓名/床位/健康状态），状态由预警引擎实时驱动（正常/关注/异常）；未读预警带角标；点击卡片进入照护工作页。</t>
         </is>
       </c>
-      <c r="G41" s="43" t="n"/>
-      <c r="H41" s="43" t="n"/>
-      <c r="I41" s="43" t="n"/>
-      <c r="J41" s="37" t="inlineStr">
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="39" t="n"/>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K41" s="38" t="inlineStr">
+      <c r="K41" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5677,30 +5133,30 @@
     </row>
     <row r="42" ht="76" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="53" t="n">
+      <c r="B42" s="49" t="n">
         <v>37</v>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="41" t="n"/>
-      <c r="E42" s="47" t="inlineStr">
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="43" t="inlineStr">
         <is>
           <t>今日待办与筛选</t>
         </is>
       </c>
-      <c r="F42" s="55" t="inlineStr">
+      <c r="F42" s="51" t="inlineStr">
         <is>
           <t>今日待办：列出测量/用药/预警处理/家属留言等待办项（含所属老人与时间），已完成置灰划线；支持按状态与按老人筛选；勾选标记完成并记录操作日志。</t>
         </is>
       </c>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="43" t="n"/>
-      <c r="I42" s="43" t="n"/>
-      <c r="J42" s="37" t="inlineStr">
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="39" t="n"/>
+      <c r="I42" s="39" t="n"/>
+      <c r="J42" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K42" s="38" t="inlineStr">
+      <c r="K42" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5708,34 +5164,34 @@
     </row>
     <row r="43" ht="104" customFormat="1" customHeight="1" s="4">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="39" t="n">
+      <c r="B43" s="35" t="n">
         <v>38</v>
       </c>
-      <c r="C43" s="40" t="n"/>
+      <c r="C43" s="36" t="n"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>预警处理</t>
         </is>
       </c>
-      <c r="E43" s="47" t="inlineStr">
+      <c r="E43" s="43" t="inlineStr">
         <is>
           <t>查看与处理预警</t>
         </is>
       </c>
-      <c r="F43" s="55" t="inlineStr">
+      <c r="F43" s="51" t="inlineStr">
         <is>
           <t>预警处理：预警卡片按风险等级降序展示（仅显示本人负责老人），详情含阈值与近30天趋势；处理需填结论（已上门查看/已通知家属/误报）并留痕，状态流转 待处理→已处理；误报结论可反馈阈值引擎作为调参参考。</t>
         </is>
       </c>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
-      <c r="J43" s="37" t="inlineStr">
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K43" s="38" t="inlineStr">
+      <c r="K43" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5743,38 +5199,38 @@
     </row>
     <row r="44" ht="76" customFormat="1" customHeight="1" s="4">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="35" t="n">
         <v>39</v>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="36" t="inlineStr">
         <is>
           <t>管理员后台</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D44" s="37" t="inlineStr">
         <is>
           <t>用户管理</t>
         </is>
       </c>
-      <c r="E44" s="67" t="inlineStr">
+      <c r="E44" s="63" t="inlineStr">
         <is>
           <t>用户与角色管理</t>
         </is>
       </c>
-      <c r="F44" s="55" t="inlineStr">
+      <c r="F44" s="51" t="inlineStr">
         <is>
           <t>用户管理：用户列表支持按角色筛选与关键字搜索；可编辑、禁用/启用、重置密码；禁用后账号即时失效并强制退出登录；仅管理员可操作，所有变更写操作日志。</t>
         </is>
       </c>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
-      <c r="J44" s="37" t="inlineStr">
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K44" s="38" t="inlineStr">
+      <c r="K44" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5782,34 +5238,34 @@
     </row>
     <row r="45" ht="90" customFormat="1" customHeight="1" s="4">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="39" t="n">
+      <c r="B45" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="C45" s="68" t="n"/>
-      <c r="D45" s="42" t="inlineStr">
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>规则配置</t>
         </is>
       </c>
-      <c r="E45" s="67" t="inlineStr">
+      <c r="E45" s="63" t="inlineStr">
         <is>
           <t>预警阈值配置</t>
         </is>
       </c>
-      <c r="F45" s="55" t="inlineStr">
+      <c r="F45" s="51" t="inlineStr">
         <is>
           <t>阈值配置：按指标（血压/心率/血氧/血糖等）列出 正常/轻度/较高/高风险 四档上下限；编辑保存前校验数值合法与档位顺序；保存即热更新至预警引擎，记录变更人与时间，可回看历史版本。</t>
         </is>
       </c>
-      <c r="G45" s="43" t="n"/>
-      <c r="H45" s="43" t="n"/>
-      <c r="I45" s="43" t="n"/>
-      <c r="J45" s="37" t="inlineStr">
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K45" s="38" t="inlineStr">
+      <c r="K45" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
@@ -5817,88 +5273,88 @@
     </row>
     <row r="46" ht="76" customFormat="1" customHeight="1" s="4">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="44" t="n">
+      <c r="B46" s="40" t="n">
         <v>41</v>
       </c>
-      <c r="C46" s="69" t="n"/>
-      <c r="D46" s="68" t="inlineStr">
+      <c r="C46" s="65" t="n"/>
+      <c r="D46" s="64" t="inlineStr">
         <is>
           <t>知识库</t>
         </is>
       </c>
-      <c r="E46" s="70" t="inlineStr">
+      <c r="E46" s="66" t="inlineStr">
         <is>
           <t>知识库维护</t>
         </is>
       </c>
-      <c r="F46" s="60" t="inlineStr">
+      <c r="F46" s="56" t="inlineStr">
         <is>
           <t>知识库维护：条目支持分类筛选与关键字搜索；可新增/编辑/发布/下架，仅“已发布”条目可被AI健康咨询引用，下架即时停止引用，操作留痕。</t>
         </is>
       </c>
-      <c r="G46" s="52" t="n"/>
-      <c r="H46" s="52" t="n"/>
-      <c r="I46" s="52" t="n"/>
-      <c r="J46" s="37" t="inlineStr">
+      <c r="G46" s="48" t="n"/>
+      <c r="H46" s="48" t="n"/>
+      <c r="I46" s="48" t="n"/>
+      <c r="J46" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K46" s="38" t="inlineStr">
+      <c r="K46" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
     <row r="47" ht="76" customFormat="1" customHeight="1" s="8">
-      <c r="A47" s="71" t="n"/>
-      <c r="B47" s="48" t="n">
+      <c r="A47" s="67" t="n"/>
+      <c r="B47" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="C47" s="72" t="n"/>
+      <c r="C47" s="68" t="n"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>统计</t>
         </is>
       </c>
-      <c r="E47" s="73" t="inlineStr">
+      <c r="E47" s="69" t="inlineStr">
         <is>
           <t>数据统计与导出</t>
         </is>
       </c>
-      <c r="F47" s="74" t="inlineStr">
+      <c r="F47" s="70" t="inlineStr">
         <is>
           <t>统计看板：展示老人总数/护工总数/今日预警数/预警处理率等指标与近30日趋势；支持选择日期范围导出Excel报表，导出记录操作人与范围，防止数据滥用。</t>
         </is>
       </c>
-      <c r="G47" s="75" t="n"/>
-      <c r="H47" s="75" t="n"/>
-      <c r="I47" s="75" t="n"/>
-      <c r="J47" s="37" t="inlineStr">
+      <c r="G47" s="71" t="n"/>
+      <c r="H47" s="71" t="n"/>
+      <c r="I47" s="71" t="n"/>
+      <c r="J47" s="33" t="inlineStr">
         <is>
           <t>周彦龙</t>
         </is>
       </c>
-      <c r="K47" s="38" t="inlineStr">
+      <c r="K47" s="34" t="inlineStr">
         <is>
           <t>组长</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="173" t="inlineStr">
+      <c r="A48" s="165" t="inlineStr">
         <is>
           <t>○：完成（通过评审或测试）　　△：进行中　　×：未着手　　N/A：不适用（没有此项活动）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="76" t="n"/>
-      <c r="C49" s="77" t="n"/>
-      <c r="D49" s="77" t="n"/>
-      <c r="E49" s="77" t="n"/>
-      <c r="F49" s="77" t="n"/>
-      <c r="G49" s="77" t="n"/>
+      <c r="B49" s="72" t="n"/>
+      <c r="C49" s="73" t="n"/>
+      <c r="D49" s="73" t="n"/>
+      <c r="E49" s="73" t="n"/>
+      <c r="F49" s="73" t="n"/>
+      <c r="G49" s="73" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5908,10 +5364,10 @@
     <mergeCell ref="A48:K48"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:I47">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"○"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0" stopIfTrue="1">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5919,7 +5375,7 @@
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="概要设计"/>
     <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="编码"/>
     <dataValidation sqref="I5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="单体测试"/>
-    <dataValidation sqref="G6:I47" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="○ ：完成&#10;△ ：进行中&#10;× ：未着手&#10;N/A：不适用" type="list">
+    <dataValidation sqref="G6:I47" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="○ ：完成_x000a_△ ：进行中_x000a_× ：未着手_x000a_N/A：不适用" type="list">
       <formula1>"○,△,×,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5943,7 +5399,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5956,7 +5412,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5969,7 +5425,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5982,7 +5438,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5995,7 +5451,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
